--- a/simulacaoes_/custo_robustez_C13/simulacao_rho000/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/custo_robustez_C13/simulacao_rho000/pre_sizing_results_optimized.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,67 +417,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>d_cm</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>esp_cm</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>bw_cm</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>h_cm</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>esp_tab_cm</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>of_volume_m3</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>of_fator_flecha</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longarina_g_m</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>longarina_g_v</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longarina_g_f</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>tabuleiro_g_m</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>longarina_g_esp</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>tabuleiro_g_esp</t>
         </is>
@@ -497,2052 +485,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.99999998327714</v>
+        <v>99.99994945119101</v>
       </c>
       <c r="B2" t="n">
-        <v>83.62960456155918</v>
+        <v>105.6554619585731</v>
       </c>
       <c r="C2" t="n">
-        <v>45.50940140657224</v>
+        <v>45.50880620292893</v>
       </c>
       <c r="D2" t="n">
-        <v>6.251316240228811</v>
+        <v>6.275199239415336</v>
       </c>
       <c r="E2" t="n">
-        <v>4.706540669169511</v>
+        <v>4.815346141534031</v>
       </c>
       <c r="F2" t="n">
-        <v>13.06119391745348</v>
+        <v>13.06605625800315</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0207014897678713</v>
+        <v>0.02070324590781733</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.8973528810605358</v>
+        <v>-0.897350331786802</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9342552085134673</v>
+        <v>-0.9342523717105923</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.961688087956648</v>
+        <v>-0.961686649964686</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.0001643739524977516</v>
+        <v>-0.007734281855985271</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6249999998745785</v>
+        <v>-0.6249996208839326</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.002089201460500484</v>
+        <v>-0.001956933984206405</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99.99999998327714</v>
+        <v>45.4283942326524</v>
       </c>
       <c r="B3" t="n">
-        <v>95.58290563757167</v>
+        <v>95.95962670665963</v>
       </c>
       <c r="C3" t="n">
-        <v>45.50940140657224</v>
+        <v>45.50388441814771</v>
       </c>
       <c r="D3" t="n">
-        <v>6.251316240228811</v>
+        <v>7.609573116019973</v>
       </c>
       <c r="E3" t="n">
-        <v>4.678220459010469</v>
+        <v>3.618983752006074</v>
       </c>
       <c r="F3" t="n">
-        <v>13.06119391745348</v>
+        <v>4.799906754623025</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0207014897678713</v>
+        <v>0.336219611004802</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8973528810605358</v>
+        <v>-0.0001723790175869402</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9342552085134673</v>
+        <v>-0.548966498688628</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.961688087956648</v>
+        <v>-0.2193749976139952</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0001643739524977516</v>
+        <v>-0.0001290880651167754</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6249999998745785</v>
+        <v>-0.552855961551016</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.002089201460500484</v>
+        <v>-0.0008632040328251933</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>45.42839339107549</v>
+        <v>45.4283942326524</v>
       </c>
       <c r="B4" t="n">
-        <v>77.62423875162703</v>
+        <v>95.41638064119236</v>
       </c>
       <c r="C4" t="n">
-        <v>45.50003714299805</v>
+        <v>45.50388441814771</v>
       </c>
       <c r="D4" t="n">
-        <v>7.60943163284696</v>
+        <v>7.609573116019973</v>
       </c>
       <c r="E4" t="n">
-        <v>3.216260076880351</v>
+        <v>4.850659423273211</v>
       </c>
       <c r="F4" t="n">
-        <v>4.799745923264973</v>
+        <v>4.799906754623025</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3362180449624018</v>
+        <v>0.336219611004802</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0001733326188015982</v>
+        <v>-0.0001723790175869402</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5489670031150805</v>
+        <v>-0.548966498688628</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2193762024326698</v>
+        <v>-0.2193749976139952</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.014747561269864e-06</v>
+        <v>-0.0001290880651167754</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5528559559405033</v>
+        <v>-0.552855961551016</v>
       </c>
       <c r="M4" t="n">
-        <v>-8.253999567442438e-06</v>
+        <v>-0.0008632040328251933</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>45.42839339107549</v>
+        <v>83.73429158276045</v>
       </c>
       <c r="B5" t="n">
-        <v>78.11019473849262</v>
+        <v>142.073100576298</v>
       </c>
       <c r="C5" t="n">
-        <v>45.50003714299805</v>
+        <v>45.56493505615403</v>
       </c>
       <c r="D5" t="n">
-        <v>7.60943163284696</v>
+        <v>8.475938107077326</v>
       </c>
       <c r="E5" t="n">
-        <v>3.891462489026085</v>
+        <v>2.541339319516931</v>
       </c>
       <c r="F5" t="n">
-        <v>4.799745923264973</v>
+        <v>9.998073298918316</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3362180449624018</v>
+        <v>0.03785624340988621</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0001733326188015982</v>
+        <v>-0.8301353818399916</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5489670031150805</v>
+        <v>-0.8950413366586948</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2193762024326698</v>
+        <v>-0.9254433988159438</v>
       </c>
       <c r="K5" t="n">
-        <v>-8.014747561269864e-06</v>
+        <v>-0.01413794565274265</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5528559559405033</v>
+        <v>-0.5030071868707033</v>
       </c>
       <c r="M5" t="n">
-        <v>-8.253999567442438e-06</v>
+        <v>-0.0144300124786724</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>84.43102917662178</v>
+        <v>76.86304728963654</v>
       </c>
       <c r="B6" t="n">
-        <v>116.061863008231</v>
+        <v>95.68125549961431</v>
       </c>
       <c r="C6" t="n">
-        <v>46.71223457554184</v>
+        <v>45.50968418637637</v>
       </c>
       <c r="D6" t="n">
-        <v>8.379487515242156</v>
+        <v>9.245476904529507</v>
       </c>
       <c r="E6" t="n">
-        <v>4.225621282726919</v>
+        <v>3.373523335594077</v>
       </c>
       <c r="F6" t="n">
-        <v>10.1595931144778</v>
+        <v>8.853528049907792</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03681559860275824</v>
+        <v>0.05120141531221502</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8340778378524702</v>
+        <v>-0.7826583924231734</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8972182789025273</v>
+        <v>-0.8694364330827479</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9277204979502396</v>
+        <v>-0.8966708538152424</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.03483960394267679</v>
+        <v>-0.01279702562733316</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5082327188246634</v>
+        <v>-0.451472854672274</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2693854612315205</v>
+        <v>-0.002152041416970396</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>72.63328552040166</v>
+        <v>69.23873154009929</v>
       </c>
       <c r="B7" t="n">
-        <v>89.92428765994795</v>
+        <v>101.7958410519354</v>
       </c>
       <c r="C7" t="n">
-        <v>47.65882996893409</v>
+        <v>45.50087317399809</v>
       </c>
       <c r="D7" t="n">
-        <v>9.689677856816504</v>
+        <v>10.20033031844927</v>
       </c>
       <c r="E7" t="n">
-        <v>4.983485501784726</v>
+        <v>4.913835860384242</v>
       </c>
       <c r="F7" t="n">
-        <v>8.293257145050012</v>
+        <v>7.736358197409261</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06291859636519914</v>
+        <v>0.07472516327808548</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7437447094703771</v>
+        <v>-0.7055973669063649</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8493626041713062</v>
+        <v>-0.830485856284075</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8714420070987133</v>
+        <v>-0.8454818644192648</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.05689155193355619</v>
+        <v>-0.04484524167382169</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4197496414030124</v>
+        <v>-0.3942904865507447</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3006500172588383</v>
+        <v>-0.0001940386662405147</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>75.00706066278127</v>
+        <v>56.94289709703057</v>
       </c>
       <c r="B8" t="n">
-        <v>88.35913362533033</v>
+        <v>146.4059426207263</v>
       </c>
       <c r="C8" t="n">
-        <v>45.50016044731785</v>
+        <v>45.50401275354228</v>
       </c>
       <c r="D8" t="n">
-        <v>9.617128927747753</v>
+        <v>11.19397419778559</v>
       </c>
       <c r="E8" t="n">
-        <v>4.637171302643781</v>
+        <v>4.744565048369997</v>
       </c>
       <c r="F8" t="n">
-        <v>8.597158876151068</v>
+        <v>6.112141045667959</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05593690693732845</v>
+        <v>0.154312073467295</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7666703172295405</v>
+        <v>-0.4779202430340678</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8610969222888768</v>
+        <v>-0.7279758466242636</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8864732401266706</v>
+        <v>-0.6694014260543856</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.04797195405138593</v>
+        <v>-0.01398114750961804</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4375529549708594</v>
+        <v>-0.3020717282277293</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.565495952373432e-05</v>
+        <v>-0.0008917230093941075</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>48.95553345720111</v>
+        <v>80.31009213446957</v>
       </c>
       <c r="B9" t="n">
-        <v>86.74563991298335</v>
+        <v>145.8154541201162</v>
       </c>
       <c r="C9" t="n">
-        <v>45.51083624009827</v>
+        <v>45.68079826841784</v>
       </c>
       <c r="D9" t="n">
-        <v>7.366735950084481</v>
+        <v>9.101671508906858</v>
       </c>
       <c r="E9" t="n">
-        <v>3.357822484078374</v>
+        <v>4.198207912669213</v>
       </c>
       <c r="F9" t="n">
-        <v>5.273338404600723</v>
+        <v>9.46935893182979</v>
       </c>
       <c r="G9" t="n">
-        <v>0.25306379657663</v>
+        <v>0.04388962773905766</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1985109568647809</v>
+        <v>-0.8084187669204864</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6202970831852007</v>
+        <v>-0.8831224993572884</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4181925354292231</v>
+        <v>-0.912564065706441</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.04628547527555325</v>
+        <v>-0.06635409608789575</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5763702230480074</v>
+        <v>-0.4773256910085217</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.002408053355171524</v>
+        <v>-0.04017739298174117</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>81.98432402350491</v>
+        <v>47.04386848672689</v>
       </c>
       <c r="B10" t="n">
-        <v>117.2060882756999</v>
+        <v>96.00230816788068</v>
       </c>
       <c r="C10" t="n">
-        <v>45.50150216304084</v>
+        <v>45.51227812163874</v>
       </c>
       <c r="D10" t="n">
-        <v>8.793306899194523</v>
+        <v>7.444863145665651</v>
       </c>
       <c r="E10" t="n">
-        <v>3.874106840526875</v>
+        <v>4.729030803217163</v>
       </c>
       <c r="F10" t="n">
-        <v>9.718986470296183</v>
+        <v>5.001116573117913</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04078151842116447</v>
+        <v>0.2942338317527304</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.819495693371953</v>
+        <v>-0.09844753531931318</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8891644974168614</v>
+        <v>-0.5837689869382262</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9191978713260076</v>
+        <v>-0.3197172146075349</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.03833300350459527</v>
+        <v>-0.006291223863894476</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4898824301762867</v>
+        <v>-0.5636257899115127</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0003338140090763941</v>
+        <v>-0.002728471475277189</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>70.63592637603955</v>
+        <v>49.01140809078225</v>
       </c>
       <c r="B11" t="n">
-        <v>91.11527510644086</v>
+        <v>95.89095013713647</v>
       </c>
       <c r="C11" t="n">
-        <v>45.5430228923716</v>
+        <v>45.53130973829148</v>
       </c>
       <c r="D11" t="n">
-        <v>9.943312283675786</v>
+        <v>7.253891058707308</v>
       </c>
       <c r="E11" t="n">
-        <v>4.24680583644774</v>
+        <v>2.359035271003591</v>
       </c>
       <c r="F11" t="n">
-        <v>7.915856807236429</v>
+        <v>5.259494546908777</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06943022592158725</v>
+        <v>0.2518246009816935</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7222859636225609</v>
+        <v>-0.201308654926637</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8386972148530178</v>
+        <v>-0.6213556769555666</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8569969095280887</v>
+        <v>-0.4209102982187247</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.02354567407420624</v>
+        <v>-0.01871309376121987</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4047694478202966</v>
+        <v>-0.5767427206052151</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.009560642749245202</v>
+        <v>-0.006957719620327707</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>68.28035202168283</v>
+        <v>79.55860414968328</v>
       </c>
       <c r="B12" t="n">
-        <v>108.06879419393</v>
+        <v>143.4101853511116</v>
       </c>
       <c r="C12" t="n">
-        <v>45.50153945828026</v>
+        <v>45.68079826841784</v>
       </c>
       <c r="D12" t="n">
-        <v>10.13428011440556</v>
+        <v>9.101671508906858</v>
       </c>
       <c r="E12" t="n">
-        <v>2.192392463889492</v>
+        <v>4.627499689716233</v>
       </c>
       <c r="F12" t="n">
-        <v>7.567596660255171</v>
+        <v>9.327823030477489</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07854366238797753</v>
+        <v>0.04535076278459454</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6934701883037978</v>
+        <v>-0.8031837238841694</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8246272307684787</v>
+        <v>-0.8803107884776642</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8369921188663955</v>
+        <v>-0.9093886090069655</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.01410341023657181</v>
+        <v>-0.04866422838652631</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.3871026401626212</v>
+        <v>-0.4716895311226246</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.0003421018400569242</v>
+        <v>-0.04017739298174117</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>50.95914915337635</v>
+        <v>61.2128086943703</v>
       </c>
       <c r="B13" t="n">
-        <v>99.03947728289548</v>
+        <v>148.9448459470932</v>
       </c>
       <c r="C13" t="n">
-        <v>45.50078124425445</v>
+        <v>45.52472213949877</v>
       </c>
       <c r="D13" t="n">
-        <v>7.127523139632075</v>
+        <v>10.73286775056457</v>
       </c>
       <c r="E13" t="n">
-        <v>2.092680424229501</v>
+        <v>4.928991400324352</v>
       </c>
       <c r="F13" t="n">
-        <v>5.53848411497734</v>
+        <v>6.613088440660976</v>
       </c>
       <c r="G13" t="n">
-        <v>0.217400245227718</v>
+        <v>0.1175706904690955</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.2880652427211001</v>
+        <v>-0.5780069911621593</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.6541066981515634</v>
+        <v>-0.7712321919835964</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5029699999726654</v>
+        <v>-0.7508348613630019</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.04957845745095681</v>
+        <v>-0.0008912614323387766</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5897276610225091</v>
+        <v>-0.3340960652077772</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.0001736098343245451</v>
+        <v>-0.005493808777504994</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95.83671506551558</v>
+        <v>50.97746306403139</v>
       </c>
       <c r="B14" t="n">
-        <v>117.6192064135642</v>
+        <v>95.93124497219337</v>
       </c>
       <c r="C14" t="n">
-        <v>45.50131431852724</v>
+        <v>45.50334640138826</v>
       </c>
       <c r="D14" t="n">
-        <v>7.017494080982538</v>
+        <v>7.133408353042649</v>
       </c>
       <c r="E14" t="n">
-        <v>4.219488561002789</v>
+        <v>4.790097707761516</v>
       </c>
       <c r="F14" t="n">
-        <v>12.25731485673738</v>
+        <v>5.542703929225769</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02386175869015609</v>
+        <v>0.217115377539584</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8842934661282633</v>
+        <v>-0.2888127818777753</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.9262964947701245</v>
+        <v>-0.6543922840310646</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.9551225439080794</v>
+        <v>-0.503662133070698</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0410110808988591</v>
+        <v>-0.05182171313377897</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5937753629913668</v>
+        <v>-0.5898497537602092</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0002920707838305336</v>
+        <v>-0.0007436447529463042</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>54.46904661434407</v>
+        <v>62.21948365390546</v>
       </c>
       <c r="B15" t="n">
-        <v>99.03706987211859</v>
+        <v>102.2170805173524</v>
       </c>
       <c r="C15" t="n">
-        <v>45.53821703660331</v>
+        <v>45.52927989645838</v>
       </c>
       <c r="D15" t="n">
-        <v>6.644790440786386</v>
+        <v>11.07552484748913</v>
       </c>
       <c r="E15" t="n">
-        <v>4.434032548449925</v>
+        <v>4.501356170291303</v>
       </c>
       <c r="F15" t="n">
-        <v>6.022023146680801</v>
+        <v>6.829898644145849</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1692047830564767</v>
+        <v>0.1110072805368685</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4149973582697465</v>
+        <v>-0.5974105961280182</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7041259644243874</v>
+        <v>-0.7798298395215137</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.6171162510099131</v>
+        <v>-0.7658883305501353</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.04550203610576155</v>
+        <v>-0.07779072254160255</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6131269774289605</v>
+        <v>-0.341646127404291</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.00849267480073565</v>
+        <v>-0.006506643657417099</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>59.57386022680782</v>
+        <v>66.00521149570045</v>
       </c>
       <c r="B16" t="n">
-        <v>108.8766058691757</v>
+        <v>148.8430936447668</v>
       </c>
       <c r="C16" t="n">
-        <v>45.52025354476439</v>
+        <v>45.50294306460022</v>
       </c>
       <c r="D16" t="n">
-        <v>11.11646007853556</v>
+        <v>10.44819852485374</v>
       </c>
       <c r="E16" t="n">
-        <v>4.620652231181527</v>
+        <v>4.706116226745055</v>
       </c>
       <c r="F16" t="n">
-        <v>6.458228293730194</v>
+        <v>7.272009086985983</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1303719282292111</v>
+        <v>0.08900876290637287</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.54277754667275</v>
+        <v>-0.6615312968844728</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.755682030372744</v>
+        <v>-0.8093899804281307</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.722803269396044</v>
+        <v>-0.8140719453704098</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.04236168250459702</v>
+        <v>-0.03147524107745013</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3218039517010587</v>
+        <v>-0.3700390862177534</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.004500787725419675</v>
+        <v>-0.0006540143556041378</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>89.12938393133415</v>
+        <v>54.12829576726256</v>
       </c>
       <c r="B17" t="n">
-        <v>114.1699300982651</v>
+        <v>95.41623760158542</v>
       </c>
       <c r="C17" t="n">
-        <v>45.75935489235375</v>
+        <v>45.63127165337841</v>
       </c>
       <c r="D17" t="n">
-        <v>8.911900574768138</v>
+        <v>6.800270141633495</v>
       </c>
       <c r="E17" t="n">
-        <v>3.874106840526875</v>
+        <v>3.39602849825551</v>
       </c>
       <c r="F17" t="n">
-        <v>11.19397267508559</v>
+        <v>5.998605191760595</v>
       </c>
       <c r="G17" t="n">
-        <v>0.03066251425352562</v>
+        <v>0.1733368844499029</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8576922985740973</v>
+        <v>-0.4040072188439551</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.910545653741443</v>
+        <v>-0.6996684389618995</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9409904643697911</v>
+        <v>-0.6075176002159575</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2439801184802429</v>
+        <v>-0.07767503646835222</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5434703794850061</v>
+        <v>-0.6108553051150838</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.05763442052305598</v>
+        <v>-0.02917147852853547</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>65.44493433059941</v>
+        <v>46.55554558940366</v>
       </c>
       <c r="B18" t="n">
-        <v>108.8766058691757</v>
+        <v>115.3623571624331</v>
       </c>
       <c r="C18" t="n">
-        <v>45.52110939045858</v>
+        <v>45.50941598214829</v>
       </c>
       <c r="D18" t="n">
-        <v>11.09721000438568</v>
+        <v>7.481573023191193</v>
       </c>
       <c r="E18" t="n">
-        <v>3.274791268941623</v>
+        <v>2.775175986399025</v>
       </c>
       <c r="F18" t="n">
-        <v>7.319044849998591</v>
+        <v>4.93674261424519</v>
       </c>
       <c r="G18" t="n">
-        <v>0.09225051196188926</v>
+        <v>0.3061493398219792</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6526226777515499</v>
+        <v>-0.07018595911146344</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8051074691288932</v>
+        <v>-0.5736585770907007</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8075002600501255</v>
+        <v>-0.2912189836395281</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1325991696653095</v>
+        <v>-0.0007873245514729962</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3658370074794957</v>
+        <v>-0.5603703039293577</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.004690975657463958</v>
+        <v>-0.002092440477397123</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>47.59365784198844</v>
+        <v>54.40330310649094</v>
       </c>
       <c r="B19" t="n">
-        <v>111.4597396391289</v>
+        <v>144.5788956697525</v>
       </c>
       <c r="C19" t="n">
-        <v>45.5008669799758</v>
+        <v>45.52065449189789</v>
       </c>
       <c r="D19" t="n">
-        <v>7.515524178861833</v>
+        <v>11.429615607365</v>
       </c>
       <c r="E19" t="n">
-        <v>3.971308368314915</v>
+        <v>4.977562881691616</v>
       </c>
       <c r="F19" t="n">
-        <v>5.096932040237214</v>
+        <v>5.828113381988258</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2817048545972454</v>
+        <v>0.1834305029462559</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1287779949659737</v>
+        <v>-0.4026900876969298</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5946975522490286</v>
+        <v>-0.6969258690431807</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3499494826661277</v>
+        <v>-0.6046221653379433</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.04152702696084373</v>
+        <v>-0.01627538078167607</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5672910522799228</v>
+        <v>-0.283024773298682</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0001926622168445247</v>
+        <v>-0.00458988708842048</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>61.02153716095569</v>
+        <v>71.53283702743046</v>
       </c>
       <c r="B20" t="n">
-        <v>105.6603639562704</v>
+        <v>154.5848271939033</v>
       </c>
       <c r="C20" t="n">
-        <v>45.50030806439188</v>
+        <v>45.50300499772999</v>
       </c>
       <c r="D20" t="n">
-        <v>10.78875515732665</v>
+        <v>10.21400706993598</v>
       </c>
       <c r="E20" t="n">
-        <v>4.916443620401382</v>
+        <v>4.644934977525545</v>
       </c>
       <c r="F20" t="n">
-        <v>6.595808460404578</v>
+        <v>8.119716963177995</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1189823177634927</v>
+        <v>0.0664752590457986</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5740854834988738</v>
+        <v>-0.7321401126087644</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7694838762450027</v>
+        <v>-0.8435445124591092</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7477512093541988</v>
+        <v>-0.8636684031196964</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.007438683692274429</v>
+        <v>-0.09054607027635686</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3326615287071677</v>
+        <v>-0.4114962777057285</v>
       </c>
       <c r="M20" t="n">
-        <v>-6.845875375097177e-05</v>
+        <v>-0.0006677772733311438</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>97.4332874065793</v>
+        <v>94.0177104169297</v>
       </c>
       <c r="B21" t="n">
-        <v>141.3835036583529</v>
+        <v>95.94534829157735</v>
       </c>
       <c r="C21" t="n">
-        <v>45.54290339790685</v>
+        <v>45.66020304140634</v>
       </c>
       <c r="D21" t="n">
-        <v>6.798555956075111</v>
+        <v>7.237058099585694</v>
       </c>
       <c r="E21" t="n">
-        <v>4.219488561002789</v>
+        <v>4.551247836310387</v>
       </c>
       <c r="F21" t="n">
-        <v>12.57728326169564</v>
+        <v>11.90059511087149</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02258102326792341</v>
+        <v>0.02544880485763189</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8895551077000515</v>
+        <v>-0.8778588834184954</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.929476929211109</v>
+        <v>-0.922444848239991</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9577978793723426</v>
+        <v>-0.9517965108761649</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0466901801124101</v>
+        <v>-0.03371956951590919</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6057496555493447</v>
+        <v>-0.5801328281269728</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.009534088423745202</v>
+        <v>-0.03560067586807464</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>77.13915584490249</v>
+        <v>74.74013186603275</v>
       </c>
       <c r="B22" t="n">
-        <v>103.9062095312482</v>
+        <v>145.7713872202787</v>
       </c>
       <c r="C22" t="n">
-        <v>45.50016044731785</v>
+        <v>46.2858201063897</v>
       </c>
       <c r="D22" t="n">
-        <v>9.398782816481033</v>
+        <v>9.483715656993718</v>
       </c>
       <c r="E22" t="n">
-        <v>4.470734969982338</v>
+        <v>4.211631102546018</v>
       </c>
       <c r="F22" t="n">
-        <v>8.934615571076703</v>
+        <v>8.556281078149366</v>
       </c>
       <c r="G22" t="n">
-        <v>0.05060518950609001</v>
+        <v>0.05665799795856909</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7848407110293707</v>
+        <v>-0.7642473052657739</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8705622444878963</v>
+        <v>-0.8598478053308231</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8980368450282143</v>
+        <v>-0.8849080376703483</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.05059640361335501</v>
+        <v>-0.03180187822066639</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4535436688367687</v>
+        <v>-0.4355509889952457</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.565495952373432e-05</v>
+        <v>-0.1746266903088231</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>58.37882237676732</v>
+        <v>92.08882117003452</v>
       </c>
       <c r="B23" t="n">
-        <v>108.8766058691757</v>
+        <v>85.55319999990213</v>
       </c>
       <c r="C23" t="n">
-        <v>45.52110939045858</v>
+        <v>46.30019861175008</v>
       </c>
       <c r="D23" t="n">
-        <v>11.11646007853556</v>
+        <v>7.526263054472096</v>
       </c>
       <c r="E23" t="n">
-        <v>4.620905134250761</v>
+        <v>3.544208814762841</v>
       </c>
       <c r="F23" t="n">
-        <v>6.292208969123752</v>
+        <v>11.55878176629078</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1405570192434751</v>
+        <v>0.02731352093798246</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5147905164243592</v>
+        <v>-0.8704531954852724</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7436133853715864</v>
+        <v>-0.9180519348089728</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7000520437215274</v>
+        <v>-0.9478953666394011</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.02340007139612491</v>
+        <v>-0.05328758660140535</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.312841167825755</v>
+        <v>-0.5656661587752589</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.004690975657463958</v>
+        <v>-0.1778219137222392</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>93.54022055982662</v>
+        <v>91.13963260498537</v>
       </c>
       <c r="B24" t="n">
-        <v>89.89126386952279</v>
+        <v>92.20941896682932</v>
       </c>
       <c r="C24" t="n">
-        <v>45.50008772038932</v>
+        <v>45.52086790195439</v>
       </c>
       <c r="D24" t="n">
-        <v>7.480433332878629</v>
+        <v>7.526263054472096</v>
       </c>
       <c r="E24" t="n">
-        <v>4.998637332665506</v>
+        <v>3.507045524841545</v>
       </c>
       <c r="F24" t="n">
-        <v>11.83970498213458</v>
+        <v>11.32749451793689</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0259061960036674</v>
+        <v>0.02826173014249086</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8760653598659414</v>
+        <v>-0.8666274402132461</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9213683108259867</v>
+        <v>-0.9158255399261611</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.950857264974806</v>
+        <v>-0.9458553223948107</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.07563840711060699</v>
+        <v>-0.004461594344873573</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5765516541986997</v>
+        <v>-0.5585472445373902</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.949341984788799e-05</v>
+        <v>-0.004637311545419853</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>52.53116889336476</v>
+        <v>64.06194143204247</v>
       </c>
       <c r="B25" t="n">
-        <v>100.1298190695178</v>
+        <v>155.646231911766</v>
       </c>
       <c r="C25" t="n">
-        <v>45.53789744187906</v>
+        <v>45.52472213949877</v>
       </c>
       <c r="D25" t="n">
-        <v>6.950273411710453</v>
+        <v>10.73286775056457</v>
       </c>
       <c r="E25" t="n">
-        <v>4.099811811052247</v>
+        <v>4.970599051543735</v>
       </c>
       <c r="F25" t="n">
-        <v>5.758903470163434</v>
+        <v>7.033580083335063</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1938979002011847</v>
+        <v>0.09947425191831964</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.3490773927019419</v>
+        <v>-0.6305337292467648</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6778098729632011</v>
+        <v>-0.7949424102011075</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5587557014791502</v>
+        <v>-0.7911280651441335</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.05783702118031189</v>
+        <v>-0.04940102573894965</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6002077926224318</v>
+        <v>-0.3554645607403185</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.008421653750902425</v>
+        <v>-0.005493808777504994</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>86.71980783169887</v>
+        <v>68.07107782483473</v>
       </c>
       <c r="B26" t="n">
-        <v>110.2648872795212</v>
+        <v>154.5848271939033</v>
       </c>
       <c r="C26" t="n">
-        <v>45.55432869703454</v>
+        <v>45.50885839647188</v>
       </c>
       <c r="D26" t="n">
-        <v>8.906282087885408</v>
+        <v>10.20033031844927</v>
       </c>
       <c r="E26" t="n">
-        <v>4.985198689674402</v>
+        <v>4.913547251749998</v>
       </c>
       <c r="F26" t="n">
-        <v>10.68541290527698</v>
+        <v>7.547840035596343</v>
       </c>
       <c r="G26" t="n">
-        <v>0.03364846536681376</v>
+        <v>0.07945714202740466</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.8461834066544242</v>
+        <v>-0.6906883992597093</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9039825421325781</v>
+        <v>-0.8232787840836873</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9346032475692363</v>
+        <v>-0.8350234155343041</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.1802923083358111</v>
+        <v>-0.02301160513553792</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.5253985587377416</v>
+        <v>-0.3855330836862605</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.01207304378545299</v>
+        <v>-0.0019685325493074</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>64.15253900907138</v>
+        <v>73.67604503361045</v>
       </c>
       <c r="B27" t="n">
-        <v>104.8186611851835</v>
+        <v>99.69989083589991</v>
       </c>
       <c r="C27" t="n">
-        <v>45.50088999574355</v>
+        <v>45.50890988063604</v>
       </c>
       <c r="D27" t="n">
-        <v>10.85432931506328</v>
+        <v>9.925816144339734</v>
       </c>
       <c r="E27" t="n">
-        <v>3.394330197817257</v>
+        <v>4.843058450180464</v>
       </c>
       <c r="F27" t="n">
-        <v>7.070983467350363</v>
+        <v>8.427608710417857</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09904609550456385</v>
+        <v>0.05971983890431711</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.6319780705512767</v>
+        <v>-0.7541753751165893</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.7955854614733008</v>
+        <v>-0.8546674816430554</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.7922002449600205</v>
+        <v>-0.8783381741530535</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.07152977832571025</v>
+        <v>-0.07984379820347939</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.3561440425680353</v>
+        <v>-0.4275703377520783</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0001977768318990603</v>
+        <v>-0.001979973474675878</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>78.03248243905864</v>
+        <v>56.14421600637379</v>
       </c>
       <c r="B28" t="n">
-        <v>106.7603833082252</v>
+        <v>146.4059426207263</v>
       </c>
       <c r="C28" t="n">
-        <v>45.53645321348249</v>
+        <v>45.53733763041619</v>
       </c>
       <c r="D28" t="n">
-        <v>9.305233294640294</v>
+        <v>11.19397419778559</v>
       </c>
       <c r="E28" t="n">
-        <v>4.291055492871172</v>
+        <v>4.792278498278157</v>
       </c>
       <c r="F28" t="n">
-        <v>9.080287550341772</v>
+        <v>6.007413337847026</v>
       </c>
       <c r="G28" t="n">
-        <v>0.04857641972396284</v>
+        <v>0.1626839474065444</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7918745683900537</v>
+        <v>-0.4557899691210373</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.8742756014760905</v>
+        <v>-0.7187401277801534</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.9024287460062594</v>
+        <v>-0.6506590072291549</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.05240449219247559</v>
+        <v>-0.002185571257382283</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.4602436182929398</v>
+        <v>-0.2960816200478035</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.008100714107219659</v>
+        <v>-0.008297251203598921</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>55.41734614480634</v>
+        <v>49.89997713503149</v>
       </c>
       <c r="B29" t="n">
-        <v>99.35532376794072</v>
+        <v>98.33698120742741</v>
       </c>
       <c r="C29" t="n">
-        <v>45.50089331304027</v>
+        <v>45.51321160738596</v>
       </c>
       <c r="D29" t="n">
-        <v>6.475602284886668</v>
+        <v>7.609573116019973</v>
       </c>
       <c r="E29" t="n">
-        <v>2.092680424229501</v>
+        <v>3.618983752006074</v>
       </c>
       <c r="F29" t="n">
-        <v>6.149950322609619</v>
+        <v>5.469807478866585</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1585955061285922</v>
+        <v>0.235838063716573</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4439929827264418</v>
+        <v>-0.2421912008889112</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.7159558095480477</v>
+        <v>-0.6365873248989561</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.6421202550376812</v>
+        <v>-0.45989677771937</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.03348843934229921</v>
+        <v>-0.1344614175991201</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.619448974298709</v>
+        <v>-0.5826665142335432</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.000198514008948325</v>
+        <v>-0.002935912752436431</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>92.7333211305255</v>
+        <v>49.82700520373885</v>
       </c>
       <c r="B30" t="n">
-        <v>109.7949641340763</v>
+        <v>98.22361221581735</v>
       </c>
       <c r="C30" t="n">
-        <v>45.55432869703454</v>
+        <v>45.51358172265796</v>
       </c>
       <c r="D30" t="n">
-        <v>7.528597641759203</v>
+        <v>7.212768576382471</v>
       </c>
       <c r="E30" t="n">
-        <v>4.985198689674402</v>
+        <v>4.483567404572513</v>
       </c>
       <c r="F30" t="n">
-        <v>11.67433151119989</v>
+        <v>5.377119061685288</v>
       </c>
       <c r="G30" t="n">
-        <v>0.02667107159184009</v>
+        <v>0.2366192802949228</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.8729944062498989</v>
+        <v>-0.2392766581135954</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.9195527887466656</v>
+        <v>-0.6355590676075002</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.9492423510879937</v>
+        <v>-0.4572047455399992</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.06069647875090329</v>
+        <v>-0.03434888651156317</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.5704999084789412</v>
+        <v>-0.5821800346915924</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.01207304378545299</v>
+        <v>-0.003018160590657487</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>45.8011578294976</v>
+        <v>52.30714705008207</v>
       </c>
       <c r="B31" t="n">
-        <v>92.60958101552933</v>
+        <v>87.00775699014822</v>
       </c>
       <c r="C31" t="n">
-        <v>45.50000579464577</v>
+        <v>45.61367896416554</v>
       </c>
       <c r="D31" t="n">
-        <v>7.60496285841413</v>
+        <v>6.813728680265795</v>
       </c>
       <c r="E31" t="n">
-        <v>3.890527506686027</v>
+        <v>4.558978869923673</v>
       </c>
       <c r="F31" t="n">
-        <v>4.852248146842282</v>
+        <v>5.696354409700879</v>
       </c>
       <c r="G31" t="n">
-        <v>0.3259408031779613</v>
+        <v>0.1968827739329274</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.02404479694135236</v>
+        <v>-0.3409398259935144</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5573213402544115</v>
+        <v>-0.6746376599745361</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.2440559054853455</v>
+        <v>-0.5514322495986389</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.01003323627795971</v>
+        <v>-0.01301688013978102</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.5553410521966506</v>
+        <v>-0.5987143136672137</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.28769905918813e-06</v>
+        <v>-0.02526199203678678</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>69.22412337487985</v>
+        <v>47.65091577162561</v>
       </c>
       <c r="B32" t="n">
-        <v>110.2266843585215</v>
+        <v>85.12917029787265</v>
       </c>
       <c r="C32" t="n">
-        <v>45.50087214965255</v>
+        <v>45.50942582357197</v>
       </c>
       <c r="D32" t="n">
-        <v>10.13625166652151</v>
+        <v>7.444863145665651</v>
       </c>
       <c r="E32" t="n">
-        <v>2.05054245152221</v>
+        <v>4.729030803217163</v>
       </c>
       <c r="F32" t="n">
-        <v>7.720854871451897</v>
+        <v>5.091317004311168</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0747493900006551</v>
+        <v>0.2803164413853473</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.7054485169086206</v>
+        <v>-0.1319393552091537</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8304230678660861</v>
+        <v>-0.5958577317917502</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.8453822417929648</v>
+        <v>-0.3530975378866993</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.03248088649378028</v>
+        <v>-0.02525351017443242</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.3941809253115989</v>
+        <v>-0.5676727718108374</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0001938110338998988</v>
+        <v>-0.002094627460438175</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>62.94572642282923</v>
+        <v>85.97379396123884</v>
       </c>
       <c r="B33" t="n">
-        <v>104.3113945130903</v>
+        <v>139.040725534192</v>
       </c>
       <c r="C33" t="n">
-        <v>45.50088999574355</v>
+        <v>45.52593854521507</v>
       </c>
       <c r="D33" t="n">
-        <v>10.85432931506328</v>
+        <v>8.252254302377956</v>
       </c>
       <c r="E33" t="n">
-        <v>3.3748803470041</v>
+        <v>4.446196986509501</v>
       </c>
       <c r="F33" t="n">
-        <v>6.890282451135068</v>
+        <v>10.39851013275421</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1061870691710131</v>
+        <v>0.03454401970104843</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.6109963665622623</v>
+        <v>-0.8424897509700479</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.786005406688793</v>
+        <v>-0.9019543176178005</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.7763366226668053</v>
+        <v>-0.9325319658343162</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.05142941408938629</v>
+        <v>-0.02348189195518701</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.3470929481712193</v>
+        <v>-0.5198034547092913</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.0001977768318990603</v>
+        <v>-0.00576412115890601</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>87.84283162203282</v>
+        <v>88.80706143120941</v>
       </c>
       <c r="B34" t="n">
-        <v>110.1916237351194</v>
+        <v>144.310960166585</v>
       </c>
       <c r="C34" t="n">
-        <v>45.55432869703454</v>
+        <v>45.53004099304393</v>
       </c>
       <c r="D34" t="n">
-        <v>9.460066957443065</v>
+        <v>8.380020959476616</v>
       </c>
       <c r="E34" t="n">
-        <v>4.985198689674402</v>
+        <v>4.745422273926588</v>
       </c>
       <c r="F34" t="n">
-        <v>11.02988757037739</v>
+        <v>11.00823480300089</v>
       </c>
       <c r="G34" t="n">
-        <v>0.03228989030576755</v>
+        <v>0.03095902677736978</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8516036500064956</v>
+        <v>-0.8563244936960633</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.907016928084429</v>
+        <v>-0.9098042645635382</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9376224679765865</v>
+        <v>-0.9402489938703299</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.2978042148174542</v>
+        <v>-0.1319256507815284</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.5338212371652461</v>
+        <v>-0.5410529607340705</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.01207304378545299</v>
+        <v>-0.006675776231983982</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>98.67199327929183</v>
+        <v>86.24012438833299</v>
       </c>
       <c r="B35" t="n">
-        <v>125.2357787461936</v>
+        <v>165.3034669478309</v>
       </c>
       <c r="C35" t="n">
-        <v>45.54064580705411</v>
+        <v>45.57485211072176</v>
       </c>
       <c r="D35" t="n">
-        <v>6.936711902387664</v>
+        <v>8.308109040283689</v>
       </c>
       <c r="E35" t="n">
-        <v>4.202709897231133</v>
+        <v>4.742637500603165</v>
       </c>
       <c r="F35" t="n">
-        <v>12.8917064627708</v>
+        <v>10.46581599665343</v>
       </c>
       <c r="G35" t="n">
-        <v>0.02167673702505856</v>
+        <v>0.03419231617355434</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8933754195565473</v>
+        <v>-0.8438565800521474</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9317873688176773</v>
+        <v>-0.9027184783414536</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.9597120553377902</v>
+        <v>-0.93330357138103</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.1344248455628749</v>
+        <v>-0.04510507014140852</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.6150399495946887</v>
+        <v>-0.5218009329124974</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.009032401567580506</v>
+        <v>-0.0166338023826143</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>47.0725176256057</v>
+        <v>66.92691310156063</v>
       </c>
       <c r="B36" t="n">
-        <v>79.34245896421614</v>
+        <v>101.7958410519354</v>
       </c>
       <c r="C36" t="n">
-        <v>45.50003714299805</v>
+        <v>45.50885839647188</v>
       </c>
       <c r="D36" t="n">
-        <v>7.60943163284696</v>
+        <v>10.20033031844927</v>
       </c>
       <c r="E36" t="n">
-        <v>3.858244137681257</v>
+        <v>4.913835860384242</v>
       </c>
       <c r="F36" t="n">
-        <v>5.038637324568851</v>
+        <v>7.365871207064173</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2938357905959761</v>
+        <v>0.08448719458405757</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.09988387952322549</v>
+        <v>-0.675060656136071</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5842520748455414</v>
+        <v>-0.8158176265164512</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.3211197602787089</v>
+        <v>-0.8238812758290612</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.04934504984978092</v>
+        <v>-0.00145251988366451</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.5638167841707047</v>
+        <v>-0.3769518482617047</v>
       </c>
       <c r="M36" t="n">
-        <v>-8.253999567442438e-06</v>
+        <v>-0.0019685325493074</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>53.48420811382923</v>
+        <v>58.43087624098682</v>
       </c>
       <c r="B37" t="n">
-        <v>96.64370321790884</v>
+        <v>158.1324403798889</v>
       </c>
       <c r="C37" t="n">
-        <v>45.5009043262549</v>
+        <v>45.52472576004311</v>
       </c>
       <c r="D37" t="n">
-        <v>6.985073340714377</v>
+        <v>11.0663752967981</v>
       </c>
       <c r="E37" t="n">
-        <v>2.092680424229501</v>
+        <v>3.112577441319275</v>
       </c>
       <c r="F37" t="n">
-        <v>5.923580145607824</v>
+        <v>6.289292740862344</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1813709725151324</v>
+        <v>0.1400361428426332</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.3825642494975414</v>
+        <v>-0.5161029961521733</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6910567269141065</v>
+        <v>-0.7441860845199247</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5886384845242263</v>
+        <v>-0.7011358762944903</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.1003513826215742</v>
+        <v>-0.01547622015931786</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.6065613874255282</v>
+        <v>-0.3132315718074011</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.0002009613899779661</v>
+        <v>-0.005494613342912902</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>48.21322124380924</v>
+        <v>63.78276356508535</v>
       </c>
       <c r="B38" t="n">
-        <v>107.4536339378618</v>
+        <v>118.8738490491524</v>
       </c>
       <c r="C38" t="n">
-        <v>45.50165153925261</v>
+        <v>45.54599681025172</v>
       </c>
       <c r="D38" t="n">
-        <v>7.320721323561258</v>
+        <v>10.48765400943621</v>
       </c>
       <c r="E38" t="n">
-        <v>3.856525970215035</v>
+        <v>4.688644749354163</v>
       </c>
       <c r="F38" t="n">
-        <v>5.150311254651928</v>
+        <v>6.942301381937424</v>
       </c>
       <c r="G38" t="n">
-        <v>0.2679851874528493</v>
+        <v>0.1008964281364471</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.1616094387237017</v>
+        <v>-0.6259556799648702</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6067003947928147</v>
+        <v>-0.7928863944398601</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.3823408187040666</v>
+        <v>-0.787709658326276</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.0100246683064992</v>
+        <v>-3.209202369137326e-05</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.5714214749587283</v>
+        <v>-0.3533707267381402</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.0003670087228017926</v>
+        <v>-0.01022151338927094</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>49.61033711566641</v>
+        <v>59.6192142015156</v>
       </c>
       <c r="B39" t="n">
-        <v>84.68189229935689</v>
+        <v>145.3246534154252</v>
       </c>
       <c r="C39" t="n">
-        <v>45.50010909659611</v>
+        <v>45.51918590822085</v>
       </c>
       <c r="D39" t="n">
-        <v>7.136974882175505</v>
+        <v>10.98717760367904</v>
       </c>
       <c r="E39" t="n">
-        <v>2.165467138250887</v>
+        <v>2.882844252048885</v>
       </c>
       <c r="F39" t="n">
-        <v>5.327320330419805</v>
+        <v>6.43806178963194</v>
       </c>
       <c r="G39" t="n">
-        <v>0.2404199959772917</v>
+        <v>0.1298706032631776</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.2295153532196827</v>
+        <v>-0.5439076826255405</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6319049443761287</v>
+        <v>-0.7562009325077778</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.4479458146968612</v>
+        <v>-0.7237291788875603</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.006084646110711091</v>
+        <v>-0.02046977713820105</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.5807355807711094</v>
+        <v>-0.322144106511367</v>
       </c>
       <c r="M39" t="n">
-        <v>-2.424368802461663e-05</v>
+        <v>-0.004263535160189263</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>51.91643726574083</v>
+        <v>59.83594450857834</v>
       </c>
       <c r="B40" t="n">
-        <v>110.8719867198382</v>
+        <v>164.5016742968964</v>
       </c>
       <c r="C40" t="n">
-        <v>45.50097180583196</v>
+        <v>45.51918590822085</v>
       </c>
       <c r="D40" t="n">
-        <v>6.924480312232795</v>
+        <v>11.04303234142136</v>
       </c>
       <c r="E40" t="n">
-        <v>4.834899831901776</v>
+        <v>4.776783117549892</v>
       </c>
       <c r="F40" t="n">
-        <v>5.651610817909902</v>
+        <v>6.480003280826152</v>
       </c>
       <c r="G40" t="n">
-        <v>0.202568400766235</v>
+        <v>0.1281936513075438</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.326171351231233</v>
+        <v>-0.5486832916654012</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6688580158772341</v>
+        <v>-0.7582689492303268</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.5380205666837951</v>
+        <v>-0.7275558505532459</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.02778832075970331</v>
+        <v>-0.03381449791848947</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.5961095817716056</v>
+        <v>-0.3237695838143375</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.0002159568515457122</v>
+        <v>-0.004263535160189263</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>79.17394878557049</v>
+        <v>71.80182528257424</v>
       </c>
       <c r="B41" t="n">
-        <v>107.1697670960581</v>
+        <v>97.51606074118421</v>
       </c>
       <c r="C41" t="n">
-        <v>43.55479076708302</v>
+        <v>45.50885821746455</v>
       </c>
       <c r="D41" t="n">
-        <v>9.458772029265294</v>
+        <v>10.21740731770868</v>
       </c>
       <c r="E41" t="n">
-        <v>4.291055492871172</v>
+        <v>4.780268685628259</v>
       </c>
       <c r="F41" t="n">
-        <v>9.424194711573051</v>
+        <v>8.166104271856662</v>
       </c>
       <c r="G41" t="n">
-        <v>0.04633859178744855</v>
+        <v>0.06559032955109606</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.8001905312451771</v>
+        <v>-0.7350333745807822</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8786229803615496</v>
+        <v>-0.8449863968984731</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9075354282893362</v>
+        <v>-0.8656160595520419</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.06722893541076629</v>
+        <v>-0.09631533361488699</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.4688046158917787</v>
+        <v>-0.4135136896193068</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.04486507810434227</v>
+        <v>-0.001968492769899993</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>80.3976375645353</v>
+        <v>53.89709288277928</v>
       </c>
       <c r="B42" t="n">
-        <v>114.1699300982651</v>
+        <v>114.304934244836</v>
       </c>
       <c r="C42" t="n">
-        <v>45.55100845681663</v>
+        <v>45.52065449189789</v>
       </c>
       <c r="D42" t="n">
-        <v>8.916561884667159</v>
+        <v>11.429615607365</v>
       </c>
       <c r="E42" t="n">
-        <v>4.811519995744855</v>
+        <v>4.800682884144334</v>
       </c>
       <c r="F42" t="n">
-        <v>9.442674295462867</v>
+        <v>5.763526830413793</v>
       </c>
       <c r="G42" t="n">
-        <v>0.04367265893311895</v>
+        <v>0.189990799764954</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.8090732427762146</v>
+        <v>-0.3860240016267524</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.8834969555345801</v>
+        <v>-0.6902066558499504</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.912965007544468</v>
+        <v>-0.5898979628916332</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.02667288706272681</v>
+        <v>-0.008665233445123374</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.4779822817340148</v>
+        <v>-0.2792281966208445</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.01133521262591752</v>
+        <v>-0.00458988708842048</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>58.52361247547114</v>
+        <v>45.88988604653483</v>
       </c>
       <c r="B43" t="n">
-        <v>108.8766058691757</v>
+        <v>95.95962670665963</v>
       </c>
       <c r="C43" t="n">
-        <v>45.52110990852583</v>
+        <v>45.7694202314314</v>
       </c>
       <c r="D43" t="n">
-        <v>11.11646007853556</v>
+        <v>7.609573116019973</v>
       </c>
       <c r="E43" t="n">
-        <v>4.893043776344636</v>
+        <v>2.411363497696808</v>
       </c>
       <c r="F43" t="n">
-        <v>6.312149840206109</v>
+        <v>4.875197020699447</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1392687852559135</v>
+        <v>0.323652525004709</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.5183031581205818</v>
+        <v>-0.02955056351250906</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.745117758984354</v>
+        <v>-0.5592455197076752</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.7029319333124988</v>
+        <v>-0.2497066810245158</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.02569972697441383</v>
+        <v>-0.01965487172871962</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.3139270935660335</v>
+        <v>-0.5559325736435656</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.004691090783517787</v>
+        <v>-0.05987116254031047</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>65.29638022705022</v>
+        <v>48.35764673096969</v>
       </c>
       <c r="B44" t="n">
-        <v>108.033334476006</v>
+        <v>90.51125925421583</v>
       </c>
       <c r="C44" t="n">
-        <v>45.50060337984141</v>
+        <v>45.50241886360033</v>
       </c>
       <c r="D44" t="n">
-        <v>10.36257793365068</v>
+        <v>7.411677445654781</v>
       </c>
       <c r="E44" t="n">
-        <v>3.193538545011473</v>
+        <v>3.690508917402973</v>
       </c>
       <c r="F44" t="n">
-        <v>7.144721729304347</v>
+        <v>5.190869148061621</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0925202034498185</v>
+        <v>0.265117817428955</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.6507684866035905</v>
+        <v>-0.1688829410233804</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.8043697525349089</v>
+        <v>-0.6093514563773471</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.8061969797828183</v>
+        <v>-0.3894328604030109</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.002447432821240176</v>
+        <v>-0.03871822702178683</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.3647228517028767</v>
+        <v>-0.572384311539798</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.0001340844092009852</v>
+        <v>-0.0005375252445161127</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>55.41734614480634</v>
+        <v>51.67182850271132</v>
       </c>
       <c r="B45" t="n">
-        <v>95.17644979406826</v>
+        <v>90.42822994643183</v>
       </c>
       <c r="C45" t="n">
-        <v>45.50089331304027</v>
+        <v>45.52071139413126</v>
       </c>
       <c r="D45" t="n">
-        <v>6.475602284886668</v>
+        <v>6.884944757100524</v>
       </c>
       <c r="E45" t="n">
-        <v>2.092680424229501</v>
+        <v>2.745698483948474</v>
       </c>
       <c r="F45" t="n">
-        <v>6.149950322609619</v>
+        <v>5.60432554102601</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1585955061285922</v>
+        <v>0.2061326143977088</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.4439929827264418</v>
+        <v>-0.3167721082424529</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.7159558095480477</v>
+        <v>-0.6652128527346711</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.6421202550376812</v>
+        <v>-0.5294476008509105</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.03348843934229921</v>
+        <v>-0.008074808003985126</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.619448974298709</v>
+        <v>-0.5944788566847421</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.000198514008948325</v>
+        <v>-0.004602532029169271</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>61.68024655476644</v>
+        <v>98.5455644251584</v>
       </c>
       <c r="B46" t="n">
-        <v>104.7035498475915</v>
+        <v>85.12917029787265</v>
       </c>
       <c r="C46" t="n">
-        <v>45.52110939045858</v>
+        <v>45.52080636065574</v>
       </c>
       <c r="D46" t="n">
-        <v>11.09404123154873</v>
+        <v>7.501425439790143</v>
       </c>
       <c r="E46" t="n">
-        <v>3.394579059890702</v>
+        <v>3.562649665536865</v>
       </c>
       <c r="F46" t="n">
-        <v>6.75457417069291</v>
+        <v>12.97739047581244</v>
       </c>
       <c r="G46" t="n">
-        <v>0.114638508294109</v>
+        <v>0.02181217766265122</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.5870191442622484</v>
+        <v>-0.8929315071393799</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7751721061069202</v>
+        <v>-0.9314855485524903</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.7578330852720744</v>
+        <v>-0.959485871345252</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.07209894639314943</v>
+        <v>-0.2549451248400481</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.3376018491607483</v>
+        <v>-0.614091733188688</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.004690975657463958</v>
+        <v>-0.004623635701274942</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>48.20077609953398</v>
+        <v>58.43087624098682</v>
       </c>
       <c r="B47" t="n">
-        <v>98.08068532745381</v>
+        <v>158.1324403798889</v>
       </c>
       <c r="C47" t="n">
-        <v>45.53577976638208</v>
+        <v>45.52472576004311</v>
       </c>
       <c r="D47" t="n">
-        <v>7.320721323561258</v>
+        <v>11.0663752967981</v>
       </c>
       <c r="E47" t="n">
-        <v>3.273842761378011</v>
+        <v>3.207639856497201</v>
       </c>
       <c r="F47" t="n">
-        <v>5.149550772542706</v>
+        <v>6.289292740862344</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2682545837121991</v>
+        <v>0.1400361428426332</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.1609649030324899</v>
+        <v>-0.5161029961521733</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.6064632169850847</v>
+        <v>-0.7441860845199247</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.3817086044665869</v>
+        <v>-0.7011358762944903</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.01035829145221522</v>
+        <v>-0.01547622015931786</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.5713385073302266</v>
+        <v>-0.3132315718074011</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.007951059196018434</v>
+        <v>-0.005494613342912902</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>46.12613049586909</v>
+        <v>95.10577533775802</v>
       </c>
       <c r="B48" t="n">
-        <v>92.60958101552933</v>
+        <v>161.5272554111559</v>
       </c>
       <c r="C48" t="n">
-        <v>45.50000579464577</v>
+        <v>45.66585314505262</v>
       </c>
       <c r="D48" t="n">
-        <v>7.581755553461614</v>
+        <v>7.237058099585694</v>
       </c>
       <c r="E48" t="n">
-        <v>4.989821039362896</v>
+        <v>4.565664371502228</v>
       </c>
       <c r="F48" t="n">
-        <v>4.894422193819151</v>
+        <v>12.14320635420495</v>
       </c>
       <c r="G48" t="n">
-        <v>0.3172736274087478</v>
+        <v>0.02449666576158704</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.04425597025279337</v>
+        <v>-0.8817474048657521</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.564443995536355</v>
+        <v>-0.9247582931408314</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.2648006372147116</v>
+        <v>-0.9538119706896853</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.01379682521994469</v>
+        <v>-0.07428574490628199</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.5575075366391273</v>
+        <v>-0.588293315033185</v>
       </c>
       <c r="M48" t="n">
-        <v>-1.28769905918813e-06</v>
+        <v>-0.03685625445613724</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>46.87524917100302</v>
+        <v>48.51495700352891</v>
       </c>
       <c r="B49" t="n">
-        <v>92.60958101552933</v>
+        <v>90.51125925421583</v>
       </c>
       <c r="C49" t="n">
-        <v>45.50000579464577</v>
+        <v>45.50077282452806</v>
       </c>
       <c r="D49" t="n">
-        <v>7.586002260988516</v>
+        <v>7.411677445654781</v>
       </c>
       <c r="E49" t="n">
-        <v>4.976978902920552</v>
+        <v>3.690508917402973</v>
       </c>
       <c r="F49" t="n">
-        <v>5.004727627048524</v>
+        <v>5.214751701176285</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2985006988892048</v>
+        <v>0.2618919911664612</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.08867657640443805</v>
+        <v>-0.1768086491047824</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.5802378378281351</v>
+        <v>-0.6122665940098462</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.3098676592704552</v>
+        <v>-0.3971578942169523</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.03751700043250737</v>
+        <v>-0.04365841475269065</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.5625016611400202</v>
+        <v>-0.5734330466901927</v>
       </c>
       <c r="M49" t="n">
-        <v>-1.28769905918813e-06</v>
+        <v>-0.0001717387840133311</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>53.20166430227511</v>
+        <v>88.29110051840973</v>
       </c>
       <c r="B50" t="n">
-        <v>99.16258837328714</v>
+        <v>88.41042484110598</v>
       </c>
       <c r="C50" t="n">
-        <v>45.50946853168658</v>
+        <v>45.53004099304393</v>
       </c>
       <c r="D50" t="n">
-        <v>6.686415071972636</v>
+        <v>8.198581788006525</v>
       </c>
       <c r="E50" t="n">
-        <v>4.998066564641635</v>
+        <v>3.167915464942932</v>
       </c>
       <c r="F50" t="n">
-        <v>5.815337143065145</v>
+        <v>10.86341110993369</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1846967989112989</v>
+        <v>0.03154935692920773</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.3730890890219968</v>
+        <v>-0.8539631327349281</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6873321740633199</v>
+        <v>-0.9084657265350043</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.5802727387562469</v>
+        <v>-0.9389508848575364</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.007532845444845051</v>
+        <v>-0.07814911460421478</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.6046777620151673</v>
+        <v>-0.537183253888073</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.002104118152573553</v>
+        <v>-0.006675776231983982</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>46.58026347030886</v>
+        <v>45.56028151435193</v>
       </c>
       <c r="B51" t="n">
-        <v>115.827174867716</v>
+        <v>77.0647913612008</v>
       </c>
       <c r="C51" t="n">
-        <v>45.76140616232158</v>
+        <v>45.50948736487062</v>
       </c>
       <c r="D51" t="n">
-        <v>7.515524178861833</v>
+        <v>7.752111571373907</v>
       </c>
       <c r="E51" t="n">
-        <v>3.967008365494227</v>
+        <v>4.722810520880293</v>
       </c>
       <c r="F51" t="n">
-        <v>4.955833985640846</v>
+        <v>4.848139398140795</v>
       </c>
       <c r="G51" t="n">
-        <v>0.3056707777545413</v>
+        <v>0.3328260908742352</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.07155433618630629</v>
+        <v>-0.008523029870320062</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5741301395776357</v>
+        <v>-0.5518509582384095</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.2925867290826629</v>
+        <v>-0.2279916651156013</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.01594916735008948</v>
+        <v>-0.04043090048572735</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.5605350898020591</v>
+        <v>-0.5537352100956796</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.05809025829368319</v>
+        <v>-0.002108303304583226</v>
       </c>
     </row>
   </sheetData>

--- a/simulacaoes_/custo_robustez_C13/simulacao_rho000/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/custo_robustez_C13/simulacao_rho000/pre_sizing_results_optimized.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,67 +429,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>d_cm</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>esp_cm</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>bw_cm</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>h_cm</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>esp_tab_cm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>of_volume_m3</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>of_fator_flecha</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>longarina_g_m</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>longarina_g_v</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>longarina_g_f</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>tabuleiro_g_m</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>longarina_g_esp</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>tabuleiro_g_esp</t>
         </is>
@@ -485,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99.99994945119101</v>
+        <v>99.99999998327714</v>
       </c>
       <c r="B2" t="n">
-        <v>105.6554619585731</v>
+        <v>83.62960456155918</v>
       </c>
       <c r="C2" t="n">
-        <v>45.50880620292893</v>
+        <v>45.50940140657224</v>
       </c>
       <c r="D2" t="n">
-        <v>6.275199239415336</v>
+        <v>6.251316240228811</v>
       </c>
       <c r="E2" t="n">
-        <v>4.815346141534031</v>
+        <v>4.706540669169511</v>
       </c>
       <c r="F2" t="n">
-        <v>13.06605625800315</v>
+        <v>13.06119391745348</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02070324590781733</v>
+        <v>0.0207014897678713</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.897350331786802</v>
+        <v>-0.8973528810605358</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9342523717105923</v>
+        <v>-0.9342552085134673</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.961686649964686</v>
+        <v>-0.961688087956648</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.007734281855985271</v>
+        <v>-0.0001643739524977516</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6249996208839326</v>
+        <v>-0.6249999998745785</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.001956933984206405</v>
+        <v>-0.002089201460500484</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>45.4283942326524</v>
+        <v>99.99999998327714</v>
       </c>
       <c r="B3" t="n">
-        <v>95.95962670665963</v>
+        <v>95.58290563757167</v>
       </c>
       <c r="C3" t="n">
-        <v>45.50388441814771</v>
+        <v>45.50940140657224</v>
       </c>
       <c r="D3" t="n">
-        <v>7.609573116019973</v>
+        <v>6.251316240228811</v>
       </c>
       <c r="E3" t="n">
-        <v>3.618983752006074</v>
+        <v>4.678220459010469</v>
       </c>
       <c r="F3" t="n">
-        <v>4.799906754623025</v>
+        <v>13.06119391745348</v>
       </c>
       <c r="G3" t="n">
-        <v>0.336219611004802</v>
+        <v>0.0207014897678713</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0001723790175869402</v>
+        <v>-0.8973528810605358</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.548966498688628</v>
+        <v>-0.9342552085134673</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.2193749976139952</v>
+        <v>-0.961688087956648</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.0001290880651167754</v>
+        <v>-0.0001643739524977516</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.552855961551016</v>
+        <v>-0.6249999998745785</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0008632040328251933</v>
+        <v>-0.002089201460500484</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>45.4283942326524</v>
+        <v>45.42839339107549</v>
       </c>
       <c r="B4" t="n">
-        <v>95.41638064119236</v>
+        <v>77.62423875162703</v>
       </c>
       <c r="C4" t="n">
-        <v>45.50388441814771</v>
+        <v>45.50003714299805</v>
       </c>
       <c r="D4" t="n">
-        <v>7.609573116019973</v>
+        <v>7.60943163284696</v>
       </c>
       <c r="E4" t="n">
-        <v>4.850659423273211</v>
+        <v>3.216260076880351</v>
       </c>
       <c r="F4" t="n">
-        <v>4.799906754623025</v>
+        <v>4.799745923264973</v>
       </c>
       <c r="G4" t="n">
-        <v>0.336219611004802</v>
+        <v>0.3362180449624018</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0001723790175869402</v>
+        <v>-0.0001733326188015982</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.548966498688628</v>
+        <v>-0.5489670031150805</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2193749976139952</v>
+        <v>-0.2193762024326698</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0001290880651167754</v>
+        <v>-8.014747561269864e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.552855961551016</v>
+        <v>-0.5528559559405033</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0008632040328251933</v>
+        <v>-8.253999567442438e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>83.73429158276045</v>
+        <v>45.42839339107549</v>
       </c>
       <c r="B5" t="n">
-        <v>142.073100576298</v>
+        <v>78.11019473849262</v>
       </c>
       <c r="C5" t="n">
-        <v>45.56493505615403</v>
+        <v>45.50003714299805</v>
       </c>
       <c r="D5" t="n">
-        <v>8.475938107077326</v>
+        <v>7.60943163284696</v>
       </c>
       <c r="E5" t="n">
-        <v>2.541339319516931</v>
+        <v>3.891462489026085</v>
       </c>
       <c r="F5" t="n">
-        <v>9.998073298918316</v>
+        <v>4.799745923264973</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03785624340988621</v>
+        <v>0.3362180449624018</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8301353818399916</v>
+        <v>-0.0001733326188015982</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8950413366586948</v>
+        <v>-0.5489670031150805</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9254433988159438</v>
+        <v>-0.2193762024326698</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.01413794565274265</v>
+        <v>-8.014747561269864e-06</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5030071868707033</v>
+        <v>-0.5528559559405033</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0144300124786724</v>
+        <v>-8.253999567442438e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>76.86304728963654</v>
+        <v>84.43102917662178</v>
       </c>
       <c r="B6" t="n">
-        <v>95.68125549961431</v>
+        <v>116.061863008231</v>
       </c>
       <c r="C6" t="n">
-        <v>45.50968418637637</v>
+        <v>46.71223457554184</v>
       </c>
       <c r="D6" t="n">
-        <v>9.245476904529507</v>
+        <v>8.379487515242156</v>
       </c>
       <c r="E6" t="n">
-        <v>3.373523335594077</v>
+        <v>4.225621282726919</v>
       </c>
       <c r="F6" t="n">
-        <v>8.853528049907792</v>
+        <v>10.1595931144778</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05120141531221502</v>
+        <v>0.03681559860275824</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7826583924231734</v>
+        <v>-0.8340778378524702</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8694364330827479</v>
+        <v>-0.8972182789025273</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8966708538152424</v>
+        <v>-0.9277204979502396</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.01279702562733316</v>
+        <v>-0.03483960394267679</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.451472854672274</v>
+        <v>-0.5082327188246634</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.002152041416970396</v>
+        <v>-0.2693854612315205</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>69.23873154009929</v>
+        <v>72.63328552040166</v>
       </c>
       <c r="B7" t="n">
-        <v>101.7958410519354</v>
+        <v>89.92428765994795</v>
       </c>
       <c r="C7" t="n">
-        <v>45.50087317399809</v>
+        <v>47.65882996893409</v>
       </c>
       <c r="D7" t="n">
-        <v>10.20033031844927</v>
+        <v>9.689677856816504</v>
       </c>
       <c r="E7" t="n">
-        <v>4.913835860384242</v>
+        <v>4.983485501784726</v>
       </c>
       <c r="F7" t="n">
-        <v>7.736358197409261</v>
+        <v>8.293257145050012</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07472516327808548</v>
+        <v>0.06291859636519914</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7055973669063649</v>
+        <v>-0.7437447094703771</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.830485856284075</v>
+        <v>-0.8493626041713062</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8454818644192648</v>
+        <v>-0.8714420070987133</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.04484524167382169</v>
+        <v>-0.05689155193355619</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3942904865507447</v>
+        <v>-0.4197496414030124</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0001940386662405147</v>
+        <v>-0.3006500172588383</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56.94289709703057</v>
+        <v>75.00706066278127</v>
       </c>
       <c r="B8" t="n">
-        <v>146.4059426207263</v>
+        <v>88.35913362533033</v>
       </c>
       <c r="C8" t="n">
-        <v>45.50401275354228</v>
+        <v>45.50016044731785</v>
       </c>
       <c r="D8" t="n">
-        <v>11.19397419778559</v>
+        <v>9.617128927747753</v>
       </c>
       <c r="E8" t="n">
-        <v>4.744565048369997</v>
+        <v>4.637171302643781</v>
       </c>
       <c r="F8" t="n">
-        <v>6.112141045667959</v>
+        <v>8.597158876151068</v>
       </c>
       <c r="G8" t="n">
-        <v>0.154312073467295</v>
+        <v>0.05593690693732845</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4779202430340678</v>
+        <v>-0.7666703172295405</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7279758466242636</v>
+        <v>-0.8610969222888768</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6694014260543856</v>
+        <v>-0.8864732401266706</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.01398114750961804</v>
+        <v>-0.04797195405138593</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3020717282277293</v>
+        <v>-0.4375529549708594</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0008917230093941075</v>
+        <v>-3.565495952373432e-05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>80.31009213446957</v>
+        <v>48.95553345720111</v>
       </c>
       <c r="B9" t="n">
-        <v>145.8154541201162</v>
+        <v>86.74563991298335</v>
       </c>
       <c r="C9" t="n">
-        <v>45.68079826841784</v>
+        <v>45.51083624009827</v>
       </c>
       <c r="D9" t="n">
-        <v>9.101671508906858</v>
+        <v>7.366735950084481</v>
       </c>
       <c r="E9" t="n">
-        <v>4.198207912669213</v>
+        <v>3.357822484078374</v>
       </c>
       <c r="F9" t="n">
-        <v>9.46935893182979</v>
+        <v>5.273338404600723</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04388962773905766</v>
+        <v>0.25306379657663</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8084187669204864</v>
+        <v>-0.1985109568647809</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8831224993572884</v>
+        <v>-0.6202970831852007</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.912564065706441</v>
+        <v>-0.4181925354292231</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.06635409608789575</v>
+        <v>-0.04628547527555325</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4773256910085217</v>
+        <v>-0.5763702230480074</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.04017739298174117</v>
+        <v>-0.002408053355171524</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>47.04386848672689</v>
+        <v>81.98432402350491</v>
       </c>
       <c r="B10" t="n">
-        <v>96.00230816788068</v>
+        <v>117.2060882756999</v>
       </c>
       <c r="C10" t="n">
-        <v>45.51227812163874</v>
+        <v>45.50150216304084</v>
       </c>
       <c r="D10" t="n">
-        <v>7.444863145665651</v>
+        <v>8.793306899194523</v>
       </c>
       <c r="E10" t="n">
-        <v>4.729030803217163</v>
+        <v>3.874106840526875</v>
       </c>
       <c r="F10" t="n">
-        <v>5.001116573117913</v>
+        <v>9.718986470296183</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2942338317527304</v>
+        <v>0.04078151842116447</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.09844753531931318</v>
+        <v>-0.819495693371953</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5837689869382262</v>
+        <v>-0.8891644974168614</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3197172146075349</v>
+        <v>-0.9191978713260076</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.006291223863894476</v>
+        <v>-0.03833300350459527</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5636257899115127</v>
+        <v>-0.4898824301762867</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.002728471475277189</v>
+        <v>-0.0003338140090763941</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>49.01140809078225</v>
+        <v>70.63592637603955</v>
       </c>
       <c r="B11" t="n">
-        <v>95.89095013713647</v>
+        <v>91.11527510644086</v>
       </c>
       <c r="C11" t="n">
-        <v>45.53130973829148</v>
+        <v>45.5430228923716</v>
       </c>
       <c r="D11" t="n">
-        <v>7.253891058707308</v>
+        <v>9.943312283675786</v>
       </c>
       <c r="E11" t="n">
-        <v>2.359035271003591</v>
+        <v>4.24680583644774</v>
       </c>
       <c r="F11" t="n">
-        <v>5.259494546908777</v>
+        <v>7.915856807236429</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2518246009816935</v>
+        <v>0.06943022592158725</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.201308654926637</v>
+        <v>-0.7222859636225609</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6213556769555666</v>
+        <v>-0.8386972148530178</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4209102982187247</v>
+        <v>-0.8569969095280887</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.01871309376121987</v>
+        <v>-0.02354567407420624</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5767427206052151</v>
+        <v>-0.4047694478202966</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.006957719620327707</v>
+        <v>-0.009560642749245202</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>79.55860414968328</v>
+        <v>68.28035202168283</v>
       </c>
       <c r="B12" t="n">
-        <v>143.4101853511116</v>
+        <v>108.06879419393</v>
       </c>
       <c r="C12" t="n">
-        <v>45.68079826841784</v>
+        <v>45.50153945828026</v>
       </c>
       <c r="D12" t="n">
-        <v>9.101671508906858</v>
+        <v>10.13428011440556</v>
       </c>
       <c r="E12" t="n">
-        <v>4.627499689716233</v>
+        <v>2.192392463889492</v>
       </c>
       <c r="F12" t="n">
-        <v>9.327823030477489</v>
+        <v>7.567596660255171</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04535076278459454</v>
+        <v>0.07854366238797753</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8031837238841694</v>
+        <v>-0.6934701883037978</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8803107884776642</v>
+        <v>-0.8246272307684787</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9093886090069655</v>
+        <v>-0.8369921188663955</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.04866422838652631</v>
+        <v>-0.01410341023657181</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.4716895311226246</v>
+        <v>-0.3871026401626212</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.04017739298174117</v>
+        <v>-0.0003421018400569242</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>61.2128086943703</v>
+        <v>50.95914915337635</v>
       </c>
       <c r="B13" t="n">
-        <v>148.9448459470932</v>
+        <v>99.03947728289548</v>
       </c>
       <c r="C13" t="n">
-        <v>45.52472213949877</v>
+        <v>45.50078124425445</v>
       </c>
       <c r="D13" t="n">
-        <v>10.73286775056457</v>
+        <v>7.127523139632075</v>
       </c>
       <c r="E13" t="n">
-        <v>4.928991400324352</v>
+        <v>2.092680424229501</v>
       </c>
       <c r="F13" t="n">
-        <v>6.613088440660976</v>
+        <v>5.53848411497734</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1175706904690955</v>
+        <v>0.217400245227718</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5780069911621593</v>
+        <v>-0.2880652427211001</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7712321919835964</v>
+        <v>-0.6541066981515634</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7508348613630019</v>
+        <v>-0.5029699999726654</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.0008912614323387766</v>
+        <v>-0.04957845745095681</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3340960652077772</v>
+        <v>-0.5897276610225091</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.005493808777504994</v>
+        <v>-0.0001736098343245451</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>50.97746306403139</v>
+        <v>95.83671506551558</v>
       </c>
       <c r="B14" t="n">
-        <v>95.93124497219337</v>
+        <v>117.6192064135642</v>
       </c>
       <c r="C14" t="n">
-        <v>45.50334640138826</v>
+        <v>45.50131431852724</v>
       </c>
       <c r="D14" t="n">
-        <v>7.133408353042649</v>
+        <v>7.017494080982538</v>
       </c>
       <c r="E14" t="n">
-        <v>4.790097707761516</v>
+        <v>4.219488561002789</v>
       </c>
       <c r="F14" t="n">
-        <v>5.542703929225769</v>
+        <v>12.25731485673738</v>
       </c>
       <c r="G14" t="n">
-        <v>0.217115377539584</v>
+        <v>0.02386175869015609</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2888127818777753</v>
+        <v>-0.8842934661282633</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6543922840310646</v>
+        <v>-0.9262964947701245</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.503662133070698</v>
+        <v>-0.9551225439080794</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.05182171313377897</v>
+        <v>-0.0410110808988591</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5898497537602092</v>
+        <v>-0.5937753629913668</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0007436447529463042</v>
+        <v>-0.0002920707838305336</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>62.21948365390546</v>
+        <v>54.46904661434407</v>
       </c>
       <c r="B15" t="n">
-        <v>102.2170805173524</v>
+        <v>99.03706987211859</v>
       </c>
       <c r="C15" t="n">
-        <v>45.52927989645838</v>
+        <v>45.53821703660331</v>
       </c>
       <c r="D15" t="n">
-        <v>11.07552484748913</v>
+        <v>6.644790440786386</v>
       </c>
       <c r="E15" t="n">
-        <v>4.501356170291303</v>
+        <v>4.434032548449925</v>
       </c>
       <c r="F15" t="n">
-        <v>6.829898644145849</v>
+        <v>6.022023146680801</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1110072805368685</v>
+        <v>0.1692047830564767</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5974105961280182</v>
+        <v>-0.4149973582697465</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7798298395215137</v>
+        <v>-0.7041259644243874</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7658883305501353</v>
+        <v>-0.6171162510099131</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.07779072254160255</v>
+        <v>-0.04550203610576155</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.341646127404291</v>
+        <v>-0.6131269774289605</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.006506643657417099</v>
+        <v>-0.00849267480073565</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66.00521149570045</v>
+        <v>59.57386022680782</v>
       </c>
       <c r="B16" t="n">
-        <v>148.8430936447668</v>
+        <v>108.8766058691757</v>
       </c>
       <c r="C16" t="n">
-        <v>45.50294306460022</v>
+        <v>45.52025354476439</v>
       </c>
       <c r="D16" t="n">
-        <v>10.44819852485374</v>
+        <v>11.11646007853556</v>
       </c>
       <c r="E16" t="n">
-        <v>4.706116226745055</v>
+        <v>4.620652231181527</v>
       </c>
       <c r="F16" t="n">
-        <v>7.272009086985983</v>
+        <v>6.458228293730194</v>
       </c>
       <c r="G16" t="n">
-        <v>0.08900876290637287</v>
+        <v>0.1303719282292111</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6615312968844728</v>
+        <v>-0.54277754667275</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8093899804281307</v>
+        <v>-0.755682030372744</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.8140719453704098</v>
+        <v>-0.722803269396044</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.03147524107745013</v>
+        <v>-0.04236168250459702</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3700390862177534</v>
+        <v>-0.3218039517010587</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0006540143556041378</v>
+        <v>-0.004500787725419675</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>54.12829576726256</v>
+        <v>89.12938393133415</v>
       </c>
       <c r="B17" t="n">
-        <v>95.41623760158542</v>
+        <v>114.1699300982651</v>
       </c>
       <c r="C17" t="n">
-        <v>45.63127165337841</v>
+        <v>45.75935489235375</v>
       </c>
       <c r="D17" t="n">
-        <v>6.800270141633495</v>
+        <v>8.911900574768138</v>
       </c>
       <c r="E17" t="n">
-        <v>3.39602849825551</v>
+        <v>3.874106840526875</v>
       </c>
       <c r="F17" t="n">
-        <v>5.998605191760595</v>
+        <v>11.19397267508559</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1733368844499029</v>
+        <v>0.03066251425352562</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4040072188439551</v>
+        <v>-0.8576922985740973</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6996684389618995</v>
+        <v>-0.910545653741443</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6075176002159575</v>
+        <v>-0.9409904643697911</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.07767503646835222</v>
+        <v>-0.2439801184802429</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6108553051150838</v>
+        <v>-0.5434703794850061</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.02917147852853547</v>
+        <v>-0.05763442052305598</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>46.55554558940366</v>
+        <v>65.44493433059941</v>
       </c>
       <c r="B18" t="n">
-        <v>115.3623571624331</v>
+        <v>108.8766058691757</v>
       </c>
       <c r="C18" t="n">
-        <v>45.50941598214829</v>
+        <v>45.52110939045858</v>
       </c>
       <c r="D18" t="n">
-        <v>7.481573023191193</v>
+        <v>11.09721000438568</v>
       </c>
       <c r="E18" t="n">
-        <v>2.775175986399025</v>
+        <v>3.274791268941623</v>
       </c>
       <c r="F18" t="n">
-        <v>4.93674261424519</v>
+        <v>7.319044849998591</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3061493398219792</v>
+        <v>0.09225051196188926</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.07018595911146344</v>
+        <v>-0.6526226777515499</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5736585770907007</v>
+        <v>-0.8051074691288932</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2912189836395281</v>
+        <v>-0.8075002600501255</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0007873245514729962</v>
+        <v>-0.1325991696653095</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5603703039293577</v>
+        <v>-0.3658370074794957</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.002092440477397123</v>
+        <v>-0.004690975657463958</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>54.40330310649094</v>
+        <v>47.59365784198844</v>
       </c>
       <c r="B19" t="n">
-        <v>144.5788956697525</v>
+        <v>111.4597396391289</v>
       </c>
       <c r="C19" t="n">
-        <v>45.52065449189789</v>
+        <v>45.5008669799758</v>
       </c>
       <c r="D19" t="n">
-        <v>11.429615607365</v>
+        <v>7.515524178861833</v>
       </c>
       <c r="E19" t="n">
-        <v>4.977562881691616</v>
+        <v>3.971308368314915</v>
       </c>
       <c r="F19" t="n">
-        <v>5.828113381988258</v>
+        <v>5.096932040237214</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1834305029462559</v>
+        <v>0.2817048545972454</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4026900876969298</v>
+        <v>-0.1287779949659737</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6969258690431807</v>
+        <v>-0.5946975522490286</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6046221653379433</v>
+        <v>-0.3499494826661277</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.01627538078167607</v>
+        <v>-0.04152702696084373</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.283024773298682</v>
+        <v>-0.5672910522799228</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.00458988708842048</v>
+        <v>-0.0001926622168445247</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>71.53283702743046</v>
+        <v>61.02153716095569</v>
       </c>
       <c r="B20" t="n">
-        <v>154.5848271939033</v>
+        <v>105.6603639562704</v>
       </c>
       <c r="C20" t="n">
-        <v>45.50300499772999</v>
+        <v>45.50030806439188</v>
       </c>
       <c r="D20" t="n">
-        <v>10.21400706993598</v>
+        <v>10.78875515732665</v>
       </c>
       <c r="E20" t="n">
-        <v>4.644934977525545</v>
+        <v>4.916443620401382</v>
       </c>
       <c r="F20" t="n">
-        <v>8.119716963177995</v>
+        <v>6.595808460404578</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0664752590457986</v>
+        <v>0.1189823177634927</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7321401126087644</v>
+        <v>-0.5740854834988738</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8435445124591092</v>
+        <v>-0.7694838762450027</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8636684031196964</v>
+        <v>-0.7477512093541988</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.09054607027635686</v>
+        <v>-0.007438683692274429</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.4114962777057285</v>
+        <v>-0.3326615287071677</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0006677772733311438</v>
+        <v>-6.845875375097177e-05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>94.0177104169297</v>
+        <v>97.4332874065793</v>
       </c>
       <c r="B21" t="n">
-        <v>95.94534829157735</v>
+        <v>141.3835036583529</v>
       </c>
       <c r="C21" t="n">
-        <v>45.66020304140634</v>
+        <v>45.54290339790685</v>
       </c>
       <c r="D21" t="n">
-        <v>7.237058099585694</v>
+        <v>6.798555956075111</v>
       </c>
       <c r="E21" t="n">
-        <v>4.551247836310387</v>
+        <v>4.219488561002789</v>
       </c>
       <c r="F21" t="n">
-        <v>11.90059511087149</v>
+        <v>12.57728326169564</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02544880485763189</v>
+        <v>0.02258102326792341</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8778588834184954</v>
+        <v>-0.8895551077000515</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.922444848239991</v>
+        <v>-0.929476929211109</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9517965108761649</v>
+        <v>-0.9577978793723426</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.03371956951590919</v>
+        <v>-0.0466901801124101</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5801328281269728</v>
+        <v>-0.6057496555493447</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.03560067586807464</v>
+        <v>-0.009534088423745202</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>74.74013186603275</v>
+        <v>77.13915584490249</v>
       </c>
       <c r="B22" t="n">
-        <v>145.7713872202787</v>
+        <v>103.9062095312482</v>
       </c>
       <c r="C22" t="n">
-        <v>46.2858201063897</v>
+        <v>45.50016044731785</v>
       </c>
       <c r="D22" t="n">
-        <v>9.483715656993718</v>
+        <v>9.398782816481033</v>
       </c>
       <c r="E22" t="n">
-        <v>4.211631102546018</v>
+        <v>4.470734969982338</v>
       </c>
       <c r="F22" t="n">
-        <v>8.556281078149366</v>
+        <v>8.934615571076703</v>
       </c>
       <c r="G22" t="n">
-        <v>0.05665799795856909</v>
+        <v>0.05060518950609001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7642473052657739</v>
+        <v>-0.7848407110293707</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8598478053308231</v>
+        <v>-0.8705622444878963</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8849080376703483</v>
+        <v>-0.8980368450282143</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.03180187822066639</v>
+        <v>-0.05059640361335501</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.4355509889952457</v>
+        <v>-0.4535436688367687</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1746266903088231</v>
+        <v>-3.565495952373432e-05</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>92.08882117003452</v>
+        <v>58.37882237676732</v>
       </c>
       <c r="B23" t="n">
-        <v>85.55319999990213</v>
+        <v>108.8766058691757</v>
       </c>
       <c r="C23" t="n">
-        <v>46.30019861175008</v>
+        <v>45.52110939045858</v>
       </c>
       <c r="D23" t="n">
-        <v>7.526263054472096</v>
+        <v>11.11646007853556</v>
       </c>
       <c r="E23" t="n">
-        <v>3.544208814762841</v>
+        <v>4.620905134250761</v>
       </c>
       <c r="F23" t="n">
-        <v>11.55878176629078</v>
+        <v>6.292208969123752</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02731352093798246</v>
+        <v>0.1405570192434751</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8704531954852724</v>
+        <v>-0.5147905164243592</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9180519348089728</v>
+        <v>-0.7436133853715864</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9478953666394011</v>
+        <v>-0.7000520437215274</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.05328758660140535</v>
+        <v>-0.02340007139612491</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5656661587752589</v>
+        <v>-0.312841167825755</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1778219137222392</v>
+        <v>-0.004690975657463958</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>91.13963260498537</v>
+        <v>93.54022055982662</v>
       </c>
       <c r="B24" t="n">
-        <v>92.20941896682932</v>
+        <v>89.89126386952279</v>
       </c>
       <c r="C24" t="n">
-        <v>45.52086790195439</v>
+        <v>45.50008772038932</v>
       </c>
       <c r="D24" t="n">
-        <v>7.526263054472096</v>
+        <v>7.480433332878629</v>
       </c>
       <c r="E24" t="n">
-        <v>3.507045524841545</v>
+        <v>4.998637332665506</v>
       </c>
       <c r="F24" t="n">
-        <v>11.32749451793689</v>
+        <v>11.83970498213458</v>
       </c>
       <c r="G24" t="n">
-        <v>0.02826173014249086</v>
+        <v>0.0259061960036674</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8666274402132461</v>
+        <v>-0.8760653598659414</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.9158255399261611</v>
+        <v>-0.9213683108259867</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9458553223948107</v>
+        <v>-0.950857264974806</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.004461594344873573</v>
+        <v>-0.07563840711060699</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5585472445373902</v>
+        <v>-0.5765516541986997</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.004637311545419853</v>
+        <v>-1.949341984788799e-05</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>64.06194143204247</v>
+        <v>52.53116889336476</v>
       </c>
       <c r="B25" t="n">
-        <v>155.646231911766</v>
+        <v>100.1298190695178</v>
       </c>
       <c r="C25" t="n">
-        <v>45.52472213949877</v>
+        <v>45.53789744187906</v>
       </c>
       <c r="D25" t="n">
-        <v>10.73286775056457</v>
+        <v>6.950273411710453</v>
       </c>
       <c r="E25" t="n">
-        <v>4.970599051543735</v>
+        <v>4.099811811052247</v>
       </c>
       <c r="F25" t="n">
-        <v>7.033580083335063</v>
+        <v>5.758903470163434</v>
       </c>
       <c r="G25" t="n">
-        <v>0.09947425191831964</v>
+        <v>0.1938979002011847</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.6305337292467648</v>
+        <v>-0.3490773927019419</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7949424102011075</v>
+        <v>-0.6778098729632011</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7911280651441335</v>
+        <v>-0.5587557014791502</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.04940102573894965</v>
+        <v>-0.05783702118031189</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3554645607403185</v>
+        <v>-0.6002077926224318</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.005493808777504994</v>
+        <v>-0.008421653750902425</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>68.07107782483473</v>
+        <v>86.71980783169887</v>
       </c>
       <c r="B26" t="n">
-        <v>154.5848271939033</v>
+        <v>110.2648872795212</v>
       </c>
       <c r="C26" t="n">
-        <v>45.50885839647188</v>
+        <v>45.55432869703454</v>
       </c>
       <c r="D26" t="n">
-        <v>10.20033031844927</v>
+        <v>8.906282087885408</v>
       </c>
       <c r="E26" t="n">
-        <v>4.913547251749998</v>
+        <v>4.985198689674402</v>
       </c>
       <c r="F26" t="n">
-        <v>7.547840035596343</v>
+        <v>10.68541290527698</v>
       </c>
       <c r="G26" t="n">
-        <v>0.07945714202740466</v>
+        <v>0.03364846536681376</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.6906883992597093</v>
+        <v>-0.8461834066544242</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8232787840836873</v>
+        <v>-0.9039825421325781</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.8350234155343041</v>
+        <v>-0.9346032475692363</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.02301160513553792</v>
+        <v>-0.1802923083358111</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.3855330836862605</v>
+        <v>-0.5253985587377416</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0019685325493074</v>
+        <v>-0.01207304378545299</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>73.67604503361045</v>
+        <v>64.15253900907138</v>
       </c>
       <c r="B27" t="n">
-        <v>99.69989083589991</v>
+        <v>104.8186611851835</v>
       </c>
       <c r="C27" t="n">
-        <v>45.50890988063604</v>
+        <v>45.50088999574355</v>
       </c>
       <c r="D27" t="n">
-        <v>9.925816144339734</v>
+        <v>10.85432931506328</v>
       </c>
       <c r="E27" t="n">
-        <v>4.843058450180464</v>
+        <v>3.394330197817257</v>
       </c>
       <c r="F27" t="n">
-        <v>8.427608710417857</v>
+        <v>7.070983467350363</v>
       </c>
       <c r="G27" t="n">
-        <v>0.05971983890431711</v>
+        <v>0.09904609550456385</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.7541753751165893</v>
+        <v>-0.6319780705512767</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.8546674816430554</v>
+        <v>-0.7955854614733008</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.8783381741530535</v>
+        <v>-0.7922002449600205</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.07984379820347939</v>
+        <v>-0.07152977832571025</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.4275703377520783</v>
+        <v>-0.3561440425680353</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.001979973474675878</v>
+        <v>-0.0001977768318990603</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>56.14421600637379</v>
+        <v>78.03248243905864</v>
       </c>
       <c r="B28" t="n">
-        <v>146.4059426207263</v>
+        <v>106.7603833082252</v>
       </c>
       <c r="C28" t="n">
-        <v>45.53733763041619</v>
+        <v>45.53645321348249</v>
       </c>
       <c r="D28" t="n">
-        <v>11.19397419778559</v>
+        <v>9.305233294640294</v>
       </c>
       <c r="E28" t="n">
-        <v>4.792278498278157</v>
+        <v>4.291055492871172</v>
       </c>
       <c r="F28" t="n">
-        <v>6.007413337847026</v>
+        <v>9.080287550341772</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1626839474065444</v>
+        <v>0.04857641972396284</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.4557899691210373</v>
+        <v>-0.7918745683900537</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.7187401277801534</v>
+        <v>-0.8742756014760905</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6506590072291549</v>
+        <v>-0.9024287460062594</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.002185571257382283</v>
+        <v>-0.05240449219247559</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.2960816200478035</v>
+        <v>-0.4602436182929398</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.008297251203598921</v>
+        <v>-0.008100714107219659</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>49.89997713503149</v>
+        <v>55.41734614480634</v>
       </c>
       <c r="B29" t="n">
-        <v>98.33698120742741</v>
+        <v>99.35532376794072</v>
       </c>
       <c r="C29" t="n">
-        <v>45.51321160738596</v>
+        <v>45.50089331304027</v>
       </c>
       <c r="D29" t="n">
-        <v>7.609573116019973</v>
+        <v>6.475602284886668</v>
       </c>
       <c r="E29" t="n">
-        <v>3.618983752006074</v>
+        <v>2.092680424229501</v>
       </c>
       <c r="F29" t="n">
-        <v>5.469807478866585</v>
+        <v>6.149950322609619</v>
       </c>
       <c r="G29" t="n">
-        <v>0.235838063716573</v>
+        <v>0.1585955061285922</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2421912008889112</v>
+        <v>-0.4439929827264418</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6365873248989561</v>
+        <v>-0.7159558095480477</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.45989677771937</v>
+        <v>-0.6421202550376812</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.1344614175991201</v>
+        <v>-0.03348843934229921</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.5826665142335432</v>
+        <v>-0.619448974298709</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.002935912752436431</v>
+        <v>-0.000198514008948325</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>49.82700520373885</v>
+        <v>92.7333211305255</v>
       </c>
       <c r="B30" t="n">
-        <v>98.22361221581735</v>
+        <v>109.7949641340763</v>
       </c>
       <c r="C30" t="n">
-        <v>45.51358172265796</v>
+        <v>45.55432869703454</v>
       </c>
       <c r="D30" t="n">
-        <v>7.212768576382471</v>
+        <v>7.528597641759203</v>
       </c>
       <c r="E30" t="n">
-        <v>4.483567404572513</v>
+        <v>4.985198689674402</v>
       </c>
       <c r="F30" t="n">
-        <v>5.377119061685288</v>
+        <v>11.67433151119989</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2366192802949228</v>
+        <v>0.02667107159184009</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2392766581135954</v>
+        <v>-0.8729944062498989</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6355590676075002</v>
+        <v>-0.9195527887466656</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4572047455399992</v>
+        <v>-0.9492423510879937</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.03434888651156317</v>
+        <v>-0.06069647875090329</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.5821800346915924</v>
+        <v>-0.5704999084789412</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.003018160590657487</v>
+        <v>-0.01207304378545299</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>52.30714705008207</v>
+        <v>45.8011578294976</v>
       </c>
       <c r="B31" t="n">
-        <v>87.00775699014822</v>
+        <v>92.60958101552933</v>
       </c>
       <c r="C31" t="n">
-        <v>45.61367896416554</v>
+        <v>45.50000579464577</v>
       </c>
       <c r="D31" t="n">
-        <v>6.813728680265795</v>
+        <v>7.60496285841413</v>
       </c>
       <c r="E31" t="n">
-        <v>4.558978869923673</v>
+        <v>3.890527506686027</v>
       </c>
       <c r="F31" t="n">
-        <v>5.696354409700879</v>
+        <v>4.852248146842282</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1968827739329274</v>
+        <v>0.3259408031779613</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3409398259935144</v>
+        <v>-0.02404479694135236</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6746376599745361</v>
+        <v>-0.5573213402544115</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.5514322495986389</v>
+        <v>-0.2440559054853455</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.01301688013978102</v>
+        <v>-0.01003323627795971</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.5987143136672137</v>
+        <v>-0.5553410521966506</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.02526199203678678</v>
+        <v>-1.28769905918813e-06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>47.65091577162561</v>
+        <v>69.22412337487985</v>
       </c>
       <c r="B32" t="n">
-        <v>85.12917029787265</v>
+        <v>110.2266843585215</v>
       </c>
       <c r="C32" t="n">
-        <v>45.50942582357197</v>
+        <v>45.50087214965255</v>
       </c>
       <c r="D32" t="n">
-        <v>7.444863145665651</v>
+        <v>10.13625166652151</v>
       </c>
       <c r="E32" t="n">
-        <v>4.729030803217163</v>
+        <v>2.05054245152221</v>
       </c>
       <c r="F32" t="n">
-        <v>5.091317004311168</v>
+        <v>7.720854871451897</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2803164413853473</v>
+        <v>0.0747493900006551</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1319393552091537</v>
+        <v>-0.7054485169086206</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5958577317917502</v>
+        <v>-0.8304230678660861</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.3530975378866993</v>
+        <v>-0.8453822417929648</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.02525351017443242</v>
+        <v>-0.03248088649378028</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.5676727718108374</v>
+        <v>-0.3941809253115989</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.002094627460438175</v>
+        <v>-0.0001938110338998988</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>85.97379396123884</v>
+        <v>62.94572642282923</v>
       </c>
       <c r="B33" t="n">
-        <v>139.040725534192</v>
+        <v>104.3113945130903</v>
       </c>
       <c r="C33" t="n">
-        <v>45.52593854521507</v>
+        <v>45.50088999574355</v>
       </c>
       <c r="D33" t="n">
-        <v>8.252254302377956</v>
+        <v>10.85432931506328</v>
       </c>
       <c r="E33" t="n">
-        <v>4.446196986509501</v>
+        <v>3.3748803470041</v>
       </c>
       <c r="F33" t="n">
-        <v>10.39851013275421</v>
+        <v>6.890282451135068</v>
       </c>
       <c r="G33" t="n">
-        <v>0.03454401970104843</v>
+        <v>0.1061870691710131</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8424897509700479</v>
+        <v>-0.6109963665622623</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9019543176178005</v>
+        <v>-0.786005406688793</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.9325319658343162</v>
+        <v>-0.7763366226668053</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.02348189195518701</v>
+        <v>-0.05142941408938629</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.5198034547092913</v>
+        <v>-0.3470929481712193</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.00576412115890601</v>
+        <v>-0.0001977768318990603</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>88.80706143120941</v>
+        <v>87.84283162203282</v>
       </c>
       <c r="B34" t="n">
-        <v>144.310960166585</v>
+        <v>110.1916237351194</v>
       </c>
       <c r="C34" t="n">
-        <v>45.53004099304393</v>
+        <v>45.55432869703454</v>
       </c>
       <c r="D34" t="n">
-        <v>8.380020959476616</v>
+        <v>9.460066957443065</v>
       </c>
       <c r="E34" t="n">
-        <v>4.745422273926588</v>
+        <v>4.985198689674402</v>
       </c>
       <c r="F34" t="n">
-        <v>11.00823480300089</v>
+        <v>11.02988757037739</v>
       </c>
       <c r="G34" t="n">
-        <v>0.03095902677736978</v>
+        <v>0.03228989030576755</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8563244936960633</v>
+        <v>-0.8516036500064956</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9098042645635382</v>
+        <v>-0.907016928084429</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9402489938703299</v>
+        <v>-0.9376224679765865</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.1319256507815284</v>
+        <v>-0.2978042148174542</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.5410529607340705</v>
+        <v>-0.5338212371652461</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.006675776231983982</v>
+        <v>-0.01207304378545299</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>86.24012438833299</v>
+        <v>98.67199327929183</v>
       </c>
       <c r="B35" t="n">
-        <v>165.3034669478309</v>
+        <v>125.2357787461936</v>
       </c>
       <c r="C35" t="n">
-        <v>45.57485211072176</v>
+        <v>45.54064580705411</v>
       </c>
       <c r="D35" t="n">
-        <v>8.308109040283689</v>
+        <v>6.936711902387664</v>
       </c>
       <c r="E35" t="n">
-        <v>4.742637500603165</v>
+        <v>4.202709897231133</v>
       </c>
       <c r="F35" t="n">
-        <v>10.46581599665343</v>
+        <v>12.8917064627708</v>
       </c>
       <c r="G35" t="n">
-        <v>0.03419231617355434</v>
+        <v>0.02167673702505856</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8438565800521474</v>
+        <v>-0.8933754195565473</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9027184783414536</v>
+        <v>-0.9317873688176773</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.93330357138103</v>
+        <v>-0.9597120553377902</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.04510507014140852</v>
+        <v>-0.1344248455628749</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.5218009329124974</v>
+        <v>-0.6150399495946887</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.0166338023826143</v>
+        <v>-0.009032401567580506</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>66.92691310156063</v>
+        <v>47.0725176256057</v>
       </c>
       <c r="B36" t="n">
-        <v>101.7958410519354</v>
+        <v>79.34245896421614</v>
       </c>
       <c r="C36" t="n">
-        <v>45.50885839647188</v>
+        <v>45.50003714299805</v>
       </c>
       <c r="D36" t="n">
-        <v>10.20033031844927</v>
+        <v>7.60943163284696</v>
       </c>
       <c r="E36" t="n">
-        <v>4.913835860384242</v>
+        <v>3.858244137681257</v>
       </c>
       <c r="F36" t="n">
-        <v>7.365871207064173</v>
+        <v>5.038637324568851</v>
       </c>
       <c r="G36" t="n">
-        <v>0.08448719458405757</v>
+        <v>0.2938357905959761</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.675060656136071</v>
+        <v>-0.09988387952322549</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8158176265164512</v>
+        <v>-0.5842520748455414</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8238812758290612</v>
+        <v>-0.3211197602787089</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.00145251988366451</v>
+        <v>-0.04934504984978092</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.3769518482617047</v>
+        <v>-0.5638167841707047</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.0019685325493074</v>
+        <v>-8.253999567442438e-06</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>58.43087624098682</v>
+        <v>53.48420811382923</v>
       </c>
       <c r="B37" t="n">
-        <v>158.1324403798889</v>
+        <v>96.64370321790884</v>
       </c>
       <c r="C37" t="n">
-        <v>45.52472576004311</v>
+        <v>45.5009043262549</v>
       </c>
       <c r="D37" t="n">
-        <v>11.0663752967981</v>
+        <v>6.985073340714377</v>
       </c>
       <c r="E37" t="n">
-        <v>3.112577441319275</v>
+        <v>2.092680424229501</v>
       </c>
       <c r="F37" t="n">
-        <v>6.289292740862344</v>
+        <v>5.923580145607824</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1400361428426332</v>
+        <v>0.1813709725151324</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.5161029961521733</v>
+        <v>-0.3825642494975414</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7441860845199247</v>
+        <v>-0.6910567269141065</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7011358762944903</v>
+        <v>-0.5886384845242263</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.01547622015931786</v>
+        <v>-0.1003513826215742</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.3132315718074011</v>
+        <v>-0.6065613874255282</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.005494613342912902</v>
+        <v>-0.0002009613899779661</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>63.78276356508535</v>
+        <v>48.21322124380924</v>
       </c>
       <c r="B38" t="n">
-        <v>118.8738490491524</v>
+        <v>107.4536339378618</v>
       </c>
       <c r="C38" t="n">
-        <v>45.54599681025172</v>
+        <v>45.50165153925261</v>
       </c>
       <c r="D38" t="n">
-        <v>10.48765400943621</v>
+        <v>7.320721323561258</v>
       </c>
       <c r="E38" t="n">
-        <v>4.688644749354163</v>
+        <v>3.856525970215035</v>
       </c>
       <c r="F38" t="n">
-        <v>6.942301381937424</v>
+        <v>5.150311254651928</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1008964281364471</v>
+        <v>0.2679851874528493</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.6259556799648702</v>
+        <v>-0.1616094387237017</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.7928863944398601</v>
+        <v>-0.6067003947928147</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.787709658326276</v>
+        <v>-0.3823408187040666</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.209202369137326e-05</v>
+        <v>-0.0100246683064992</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.3533707267381402</v>
+        <v>-0.5714214749587283</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.01022151338927094</v>
+        <v>-0.0003670087228017926</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>59.6192142015156</v>
+        <v>49.61033711566641</v>
       </c>
       <c r="B39" t="n">
-        <v>145.3246534154252</v>
+        <v>84.68189229935689</v>
       </c>
       <c r="C39" t="n">
-        <v>45.51918590822085</v>
+        <v>45.50010909659611</v>
       </c>
       <c r="D39" t="n">
-        <v>10.98717760367904</v>
+        <v>7.136974882175505</v>
       </c>
       <c r="E39" t="n">
-        <v>2.882844252048885</v>
+        <v>2.165467138250887</v>
       </c>
       <c r="F39" t="n">
-        <v>6.43806178963194</v>
+        <v>5.327320330419805</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1298706032631776</v>
+        <v>0.2404199959772917</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.5439076826255405</v>
+        <v>-0.2295153532196827</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7562009325077778</v>
+        <v>-0.6319049443761287</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.7237291788875603</v>
+        <v>-0.4479458146968612</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.02046977713820105</v>
+        <v>-0.006084646110711091</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.322144106511367</v>
+        <v>-0.5807355807711094</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.004263535160189263</v>
+        <v>-2.424368802461663e-05</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>59.83594450857834</v>
+        <v>51.91643726574083</v>
       </c>
       <c r="B40" t="n">
-        <v>164.5016742968964</v>
+        <v>110.8719867198382</v>
       </c>
       <c r="C40" t="n">
-        <v>45.51918590822085</v>
+        <v>45.50097180583196</v>
       </c>
       <c r="D40" t="n">
-        <v>11.04303234142136</v>
+        <v>6.924480312232795</v>
       </c>
       <c r="E40" t="n">
-        <v>4.776783117549892</v>
+        <v>4.834899831901776</v>
       </c>
       <c r="F40" t="n">
-        <v>6.480003280826152</v>
+        <v>5.651610817909902</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1281936513075438</v>
+        <v>0.202568400766235</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.5486832916654012</v>
+        <v>-0.326171351231233</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7582689492303268</v>
+        <v>-0.6688580158772341</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.7275558505532459</v>
+        <v>-0.5380205666837951</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.03381449791848947</v>
+        <v>-0.02778832075970331</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.3237695838143375</v>
+        <v>-0.5961095817716056</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.004263535160189263</v>
+        <v>-0.0002159568515457122</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>71.80182528257424</v>
+        <v>79.17394878557049</v>
       </c>
       <c r="B41" t="n">
-        <v>97.51606074118421</v>
+        <v>107.1697670960581</v>
       </c>
       <c r="C41" t="n">
-        <v>45.50885821746455</v>
+        <v>43.55479076708302</v>
       </c>
       <c r="D41" t="n">
-        <v>10.21740731770868</v>
+        <v>9.458772029265294</v>
       </c>
       <c r="E41" t="n">
-        <v>4.780268685628259</v>
+        <v>4.291055492871172</v>
       </c>
       <c r="F41" t="n">
-        <v>8.166104271856662</v>
+        <v>9.424194711573051</v>
       </c>
       <c r="G41" t="n">
-        <v>0.06559032955109606</v>
+        <v>0.04633859178744855</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.7350333745807822</v>
+        <v>-0.8001905312451771</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8449863968984731</v>
+        <v>-0.8786229803615496</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8656160595520419</v>
+        <v>-0.9075354282893362</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.09631533361488699</v>
+        <v>-0.06722893541076629</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.4135136896193068</v>
+        <v>-0.4688046158917787</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.001968492769899993</v>
+        <v>-0.04486507810434227</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>53.89709288277928</v>
+        <v>80.3976375645353</v>
       </c>
       <c r="B42" t="n">
-        <v>114.304934244836</v>
+        <v>114.1699300982651</v>
       </c>
       <c r="C42" t="n">
-        <v>45.52065449189789</v>
+        <v>45.55100845681663</v>
       </c>
       <c r="D42" t="n">
-        <v>11.429615607365</v>
+        <v>8.916561884667159</v>
       </c>
       <c r="E42" t="n">
-        <v>4.800682884144334</v>
+        <v>4.811519995744855</v>
       </c>
       <c r="F42" t="n">
-        <v>5.763526830413793</v>
+        <v>9.442674295462867</v>
       </c>
       <c r="G42" t="n">
-        <v>0.189990799764954</v>
+        <v>0.04367265893311895</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.3860240016267524</v>
+        <v>-0.8090732427762146</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.6902066558499504</v>
+        <v>-0.8834969555345801</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.5898979628916332</v>
+        <v>-0.912965007544468</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.008665233445123374</v>
+        <v>-0.02667288706272681</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.2792281966208445</v>
+        <v>-0.4779822817340148</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.00458988708842048</v>
+        <v>-0.01133521262591752</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>45.88988604653483</v>
+        <v>58.52361247547114</v>
       </c>
       <c r="B43" t="n">
-        <v>95.95962670665963</v>
+        <v>108.8766058691757</v>
       </c>
       <c r="C43" t="n">
-        <v>45.7694202314314</v>
+        <v>45.52110990852583</v>
       </c>
       <c r="D43" t="n">
-        <v>7.609573116019973</v>
+        <v>11.11646007853556</v>
       </c>
       <c r="E43" t="n">
-        <v>2.411363497696808</v>
+        <v>4.893043776344636</v>
       </c>
       <c r="F43" t="n">
-        <v>4.875197020699447</v>
+        <v>6.312149840206109</v>
       </c>
       <c r="G43" t="n">
-        <v>0.323652525004709</v>
+        <v>0.1392687852559135</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.02955056351250906</v>
+        <v>-0.5183031581205818</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5592455197076752</v>
+        <v>-0.745117758984354</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.2497066810245158</v>
+        <v>-0.7029319333124988</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.01965487172871962</v>
+        <v>-0.02569972697441383</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.5559325736435656</v>
+        <v>-0.3139270935660335</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.05987116254031047</v>
+        <v>-0.004691090783517787</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>48.35764673096969</v>
+        <v>65.29638022705022</v>
       </c>
       <c r="B44" t="n">
-        <v>90.51125925421583</v>
+        <v>108.033334476006</v>
       </c>
       <c r="C44" t="n">
-        <v>45.50241886360033</v>
+        <v>45.50060337984141</v>
       </c>
       <c r="D44" t="n">
-        <v>7.411677445654781</v>
+        <v>10.36257793365068</v>
       </c>
       <c r="E44" t="n">
-        <v>3.690508917402973</v>
+        <v>3.193538545011473</v>
       </c>
       <c r="F44" t="n">
-        <v>5.190869148061621</v>
+        <v>7.144721729304347</v>
       </c>
       <c r="G44" t="n">
-        <v>0.265117817428955</v>
+        <v>0.0925202034498185</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.1688829410233804</v>
+        <v>-0.6507684866035905</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.6093514563773471</v>
+        <v>-0.8043697525349089</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.3894328604030109</v>
+        <v>-0.8061969797828183</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.03871822702178683</v>
+        <v>-0.002447432821240176</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.572384311539798</v>
+        <v>-0.3647228517028767</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.0005375252445161127</v>
+        <v>-0.0001340844092009852</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>51.67182850271132</v>
+        <v>55.41734614480634</v>
       </c>
       <c r="B45" t="n">
-        <v>90.42822994643183</v>
+        <v>95.17644979406826</v>
       </c>
       <c r="C45" t="n">
-        <v>45.52071139413126</v>
+        <v>45.50089331304027</v>
       </c>
       <c r="D45" t="n">
-        <v>6.884944757100524</v>
+        <v>6.475602284886668</v>
       </c>
       <c r="E45" t="n">
-        <v>2.745698483948474</v>
+        <v>2.092680424229501</v>
       </c>
       <c r="F45" t="n">
-        <v>5.60432554102601</v>
+        <v>6.149950322609619</v>
       </c>
       <c r="G45" t="n">
-        <v>0.2061326143977088</v>
+        <v>0.1585955061285922</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.3167721082424529</v>
+        <v>-0.4439929827264418</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.6652128527346711</v>
+        <v>-0.7159558095480477</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.5294476008509105</v>
+        <v>-0.6421202550376812</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.008074808003985126</v>
+        <v>-0.03348843934229921</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.5944788566847421</v>
+        <v>-0.619448974298709</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.004602532029169271</v>
+        <v>-0.000198514008948325</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>98.5455644251584</v>
+        <v>61.68024655476644</v>
       </c>
       <c r="B46" t="n">
-        <v>85.12917029787265</v>
+        <v>104.7035498475915</v>
       </c>
       <c r="C46" t="n">
-        <v>45.52080636065574</v>
+        <v>45.52110939045858</v>
       </c>
       <c r="D46" t="n">
-        <v>7.501425439790143</v>
+        <v>11.09404123154873</v>
       </c>
       <c r="E46" t="n">
-        <v>3.562649665536865</v>
+        <v>3.394579059890702</v>
       </c>
       <c r="F46" t="n">
-        <v>12.97739047581244</v>
+        <v>6.75457417069291</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02181217766265122</v>
+        <v>0.114638508294109</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.8929315071393799</v>
+        <v>-0.5870191442622484</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9314855485524903</v>
+        <v>-0.7751721061069202</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.959485871345252</v>
+        <v>-0.7578330852720744</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.2549451248400481</v>
+        <v>-0.07209894639314943</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.614091733188688</v>
+        <v>-0.3376018491607483</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.004623635701274942</v>
+        <v>-0.004690975657463958</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>58.43087624098682</v>
+        <v>48.20077609953398</v>
       </c>
       <c r="B47" t="n">
-        <v>158.1324403798889</v>
+        <v>98.08068532745381</v>
       </c>
       <c r="C47" t="n">
-        <v>45.52472576004311</v>
+        <v>45.53577976638208</v>
       </c>
       <c r="D47" t="n">
-        <v>11.0663752967981</v>
+        <v>7.320721323561258</v>
       </c>
       <c r="E47" t="n">
-        <v>3.207639856497201</v>
+        <v>3.273842761378011</v>
       </c>
       <c r="F47" t="n">
-        <v>6.289292740862344</v>
+        <v>5.149550772542706</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1400361428426332</v>
+        <v>0.2682545837121991</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.5161029961521733</v>
+        <v>-0.1609649030324899</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.7441860845199247</v>
+        <v>-0.6064632169850847</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.7011358762944903</v>
+        <v>-0.3817086044665869</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.01547622015931786</v>
+        <v>-0.01035829145221522</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.3132315718074011</v>
+        <v>-0.5713385073302266</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.005494613342912902</v>
+        <v>-0.007951059196018434</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>95.10577533775802</v>
+        <v>46.12613049586909</v>
       </c>
       <c r="B48" t="n">
-        <v>161.5272554111559</v>
+        <v>92.60958101552933</v>
       </c>
       <c r="C48" t="n">
-        <v>45.66585314505262</v>
+        <v>45.50000579464577</v>
       </c>
       <c r="D48" t="n">
-        <v>7.237058099585694</v>
+        <v>7.581755553461614</v>
       </c>
       <c r="E48" t="n">
-        <v>4.565664371502228</v>
+        <v>4.989821039362896</v>
       </c>
       <c r="F48" t="n">
-        <v>12.14320635420495</v>
+        <v>4.894422193819151</v>
       </c>
       <c r="G48" t="n">
-        <v>0.02449666576158704</v>
+        <v>0.3172736274087478</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.8817474048657521</v>
+        <v>-0.04425597025279337</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9247582931408314</v>
+        <v>-0.564443995536355</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9538119706896853</v>
+        <v>-0.2648006372147116</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.07428574490628199</v>
+        <v>-0.01379682521994469</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.588293315033185</v>
+        <v>-0.5575075366391273</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.03685625445613724</v>
+        <v>-1.28769905918813e-06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48.51495700352891</v>
+        <v>46.87524917100302</v>
       </c>
       <c r="B49" t="n">
-        <v>90.51125925421583</v>
+        <v>92.60958101552933</v>
       </c>
       <c r="C49" t="n">
-        <v>45.50077282452806</v>
+        <v>45.50000579464577</v>
       </c>
       <c r="D49" t="n">
-        <v>7.411677445654781</v>
+        <v>7.586002260988516</v>
       </c>
       <c r="E49" t="n">
-        <v>3.690508917402973</v>
+        <v>4.976978902920552</v>
       </c>
       <c r="F49" t="n">
-        <v>5.214751701176285</v>
+        <v>5.004727627048524</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2618919911664612</v>
+        <v>0.2985006988892048</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.1768086491047824</v>
+        <v>-0.08867657640443805</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.6122665940098462</v>
+        <v>-0.5802378378281351</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.3971578942169523</v>
+        <v>-0.3098676592704552</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.04365841475269065</v>
+        <v>-0.03751700043250737</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.5734330466901927</v>
+        <v>-0.5625016611400202</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0001717387840133311</v>
+        <v>-1.28769905918813e-06</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>88.29110051840973</v>
+        <v>53.20166430227511</v>
       </c>
       <c r="B50" t="n">
-        <v>88.41042484110598</v>
+        <v>99.16258837328714</v>
       </c>
       <c r="C50" t="n">
-        <v>45.53004099304393</v>
+        <v>45.50946853168658</v>
       </c>
       <c r="D50" t="n">
-        <v>8.198581788006525</v>
+        <v>6.686415071972636</v>
       </c>
       <c r="E50" t="n">
-        <v>3.167915464942932</v>
+        <v>4.998066564641635</v>
       </c>
       <c r="F50" t="n">
-        <v>10.86341110993369</v>
+        <v>5.815337143065145</v>
       </c>
       <c r="G50" t="n">
-        <v>0.03154935692920773</v>
+        <v>0.1846967989112989</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.8539631327349281</v>
+        <v>-0.3730890890219968</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.9084657265350043</v>
+        <v>-0.6873321740633199</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.9389508848575364</v>
+        <v>-0.5802727387562469</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.07814911460421478</v>
+        <v>-0.007532845444845051</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.537183253888073</v>
+        <v>-0.6046777620151673</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.006675776231983982</v>
+        <v>-0.002104118152573553</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>45.56028151435193</v>
+        <v>46.58026347030886</v>
       </c>
       <c r="B51" t="n">
-        <v>77.0647913612008</v>
+        <v>115.827174867716</v>
       </c>
       <c r="C51" t="n">
-        <v>45.50948736487062</v>
+        <v>45.76140616232158</v>
       </c>
       <c r="D51" t="n">
-        <v>7.752111571373907</v>
+        <v>7.515524178861833</v>
       </c>
       <c r="E51" t="n">
-        <v>4.722810520880293</v>
+        <v>3.967008365494227</v>
       </c>
       <c r="F51" t="n">
-        <v>4.848139398140795</v>
+        <v>4.955833985640846</v>
       </c>
       <c r="G51" t="n">
-        <v>0.3328260908742352</v>
+        <v>0.3056707777545413</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.008523029870320062</v>
+        <v>-0.07155433618630629</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5518509582384095</v>
+        <v>-0.5741301395776357</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.2279916651156013</v>
+        <v>-0.2925867290826629</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.04043090048572735</v>
+        <v>-0.01594916735008948</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.5537352100956796</v>
+        <v>-0.5605350898020591</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.002108303304583226</v>
+        <v>-0.05809025829368319</v>
       </c>
     </row>
   </sheetData>
